--- a/department-course-clustering/templates/card_sorting/CardSorting_master_improved.xlsx
+++ b/department-course-clustering/templates/card_sorting/CardSorting_master_improved.xlsx
@@ -416,7 +416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -555,6 +555,8 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -818,7 +820,7 @@
       </c>
       <c r="B2" s="34" t="inlineStr">
         <is>
-          <t>Copy Evaluation!C6:C29 from each individual response workbook.</t>
+          <t>Copy Evaluation!C6:C30 from each individual response workbook.</t>
         </is>
       </c>
     </row>
@@ -980,7 +982,7 @@
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>제시된 24개 학과를 "비슷한 성격의 학과끼리" 자유롭게 묶어주세요.</t>
+          <t>제시된 25개 학과를 "비슷한 성격의 학과끼리" 자유롭게 묶어주세요.</t>
         </is>
       </c>
     </row>
@@ -1962,6 +1964,34 @@
         <v/>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="38" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="39" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="C30" s="40" t="n"/>
+      <c r="D30" s="40" t="n"/>
+      <c r="E30" s="40" t="n"/>
+      <c r="F30" s="40" t="n"/>
+      <c r="G30" s="40" t="n"/>
+      <c r="H30" s="40" t="n"/>
+      <c r="I30" s="40" t="n"/>
+      <c r="J30" s="40" t="n"/>
+      <c r="K30" s="40" t="n"/>
+      <c r="L30" s="40" t="n"/>
+      <c r="M30" s="40" t="n"/>
+      <c r="N30" s="40" t="n"/>
+      <c r="O30" s="40" t="n"/>
+      <c r="P30" s="40" t="n"/>
+      <c r="R30" s="42">
+        <f>COUNTA(C30:P30)</f>
+        <v/>
+      </c>
+    </row>
     <row r="31" ht="24.75" customHeight="1">
       <c r="B31" s="11" t="inlineStr">
         <is>
@@ -1990,59 +2020,59 @@
         </is>
       </c>
       <c r="C32" s="17">
-        <f>COUNTA(C6:C29)/24</f>
+        <f>COUNTA(C6:C30)/25</f>
         <v/>
       </c>
       <c r="D32" s="17">
-        <f>COUNTA(D6:D29)/24</f>
+        <f>COUNTA(D6:D30)/25</f>
         <v/>
       </c>
       <c r="E32" s="17">
-        <f>COUNTA(E6:E29)/24</f>
+        <f>COUNTA(E6:E30)/25</f>
         <v/>
       </c>
       <c r="F32" s="17">
-        <f>COUNTA(F6:F29)/24</f>
+        <f>COUNTA(F6:F30)/25</f>
         <v/>
       </c>
       <c r="G32" s="17">
-        <f>COUNTA(G6:G29)/24</f>
+        <f>COUNTA(G6:G30)/25</f>
         <v/>
       </c>
       <c r="H32" s="17">
-        <f>COUNTA(H6:H29)/24</f>
+        <f>COUNTA(H6:H30)/25</f>
         <v/>
       </c>
       <c r="I32" s="17">
-        <f>COUNTA(I6:I29)/24</f>
+        <f>COUNTA(I6:I30)/25</f>
         <v/>
       </c>
       <c r="J32" s="17">
-        <f>COUNTA(J6:J29)/24</f>
+        <f>COUNTA(J6:J30)/25</f>
         <v/>
       </c>
       <c r="K32" s="17">
-        <f>COUNTA(K6:K29)/24</f>
+        <f>COUNTA(K6:K30)/25</f>
         <v/>
       </c>
       <c r="L32" s="17">
-        <f>COUNTA(L6:L29)/24</f>
+        <f>COUNTA(L6:L30)/25</f>
         <v/>
       </c>
       <c r="M32" s="17">
-        <f>COUNTA(M6:M29)/24</f>
+        <f>COUNTA(M6:M30)/25</f>
         <v/>
       </c>
       <c r="N32" s="17">
-        <f>COUNTA(N6:N29)/24</f>
+        <f>COUNTA(N6:N30)/25</f>
         <v/>
       </c>
       <c r="O32" s="17">
-        <f>COUNTA(O6:O29)/24</f>
+        <f>COUNTA(O6:O30)/25</f>
         <v/>
       </c>
       <c r="P32" s="17">
-        <f>COUNTA(P6:P29)/24</f>
+        <f>COUNTA(P6:P30)/25</f>
         <v/>
       </c>
     </row>
@@ -2054,11 +2084,11 @@
     <mergeCell ref="A1:S1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C6:P29" showDropDown="1" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="그룹 번호 확인" error="1~24 사이의 정수 그룹 번호를 입력하세요. 같은 그룹은 같은 번호를 사용합니다." type="whole" errorStyle="warning">
+    <dataValidation sqref="C6:P30" showDropDown="1" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="그룹 번호 확인" error="1~24 사이의 정수 그룹 번호를 입력하세요. 같은 그룹은 같은 번호를 사용합니다." type="whole" errorStyle="warning">
       <formula1>1</formula1>
       <formula2>24</formula2>
     </dataValidation>
-    <dataValidation sqref="C6:P29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Check input" error="Please enter an integer from 1 to 24." promptTitle="Master input" prompt="Within each respondent column, the same number means the same group." type="whole" operator="between">
+    <dataValidation sqref="C6:P30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Check input" error="Please enter an integer from 1 to 24." promptTitle="Master input" prompt="Within each respondent column, the same number means the same group." type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>24</formula2>
     </dataValidation>
@@ -2074,11 +2104,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y28"/>
+  <dimension ref="A1:Z29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="25"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="34.5" customHeight="1">
@@ -2221,6 +2253,11 @@
           <t>컴퓨터공학과</t>
         </is>
       </c>
+      <c r="Z4" s="13" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
@@ -2324,6 +2361,10 @@
         <f>IFERROR(SUMPRODUCT((평가!C6:P6&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")*(평가!C6:P6=평가!C29:P29))/SUMPRODUCT((평가!C6:P6&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")),"")</f>
         <v/>
       </c>
+      <c r="Z5" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C6:P6&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")*(평가!C6:P6=평가!C30:P30))/SUMPRODUCT((평가!C6:P6&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
@@ -2427,6 +2468,10 @@
         <f>IFERROR(SUMPRODUCT((평가!C7:P7&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")*(평가!C7:P7=평가!C29:P29))/SUMPRODUCT((평가!C7:P7&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")),"")</f>
         <v/>
       </c>
+      <c r="Z6" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C7:P7&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")*(평가!C7:P7=평가!C30:P30))/SUMPRODUCT((평가!C7:P7&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
@@ -2530,6 +2575,10 @@
         <f>IFERROR(SUMPRODUCT((평가!C8:P8&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")*(평가!C8:P8=평가!C29:P29))/SUMPRODUCT((평가!C8:P8&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")),"")</f>
         <v/>
       </c>
+      <c r="Z7" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C8:P8&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")*(평가!C8:P8=평가!C30:P30))/SUMPRODUCT((평가!C8:P8&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
@@ -2633,6 +2682,10 @@
         <f>IFERROR(SUMPRODUCT((평가!C9:P9&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")*(평가!C9:P9=평가!C29:P29))/SUMPRODUCT((평가!C9:P9&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")),"")</f>
         <v/>
       </c>
+      <c r="Z8" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C9:P9&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")*(평가!C9:P9=평가!C30:P30))/SUMPRODUCT((평가!C9:P9&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
@@ -2736,6 +2789,10 @@
         <f>IFERROR(SUMPRODUCT((평가!C10:P10&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")*(평가!C10:P10=평가!C29:P29))/SUMPRODUCT((평가!C10:P10&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")),"")</f>
         <v/>
       </c>
+      <c r="Z9" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C10:P10&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")*(평가!C10:P10=평가!C30:P30))/SUMPRODUCT((평가!C10:P10&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
@@ -2839,6 +2896,10 @@
         <f>IFERROR(SUMPRODUCT((평가!C11:P11&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")*(평가!C11:P11=평가!C29:P29))/SUMPRODUCT((평가!C11:P11&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")),"")</f>
         <v/>
       </c>
+      <c r="Z10" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C11:P11&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")*(평가!C11:P11=평가!C30:P30))/SUMPRODUCT((평가!C11:P11&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="14" t="inlineStr">
@@ -2942,6 +3003,10 @@
         <f>IFERROR(SUMPRODUCT((평가!C12:P12&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")*(평가!C12:P12=평가!C29:P29))/SUMPRODUCT((평가!C12:P12&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")),"")</f>
         <v/>
       </c>
+      <c r="Z11" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C12:P12&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")*(평가!C12:P12=평가!C30:P30))/SUMPRODUCT((평가!C12:P12&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
@@ -3045,6 +3110,10 @@
         <f>IFERROR(SUMPRODUCT((평가!C13:P13&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")*(평가!C13:P13=평가!C29:P29))/SUMPRODUCT((평가!C13:P13&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")),"")</f>
         <v/>
       </c>
+      <c r="Z12" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C13:P13&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")*(평가!C13:P13=평가!C30:P30))/SUMPRODUCT((평가!C13:P13&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
@@ -3148,6 +3217,10 @@
         <f>IFERROR(SUMPRODUCT((평가!C14:P14&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")*(평가!C14:P14=평가!C29:P29))/SUMPRODUCT((평가!C14:P14&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")),"")</f>
         <v/>
       </c>
+      <c r="Z13" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C14:P14&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")*(평가!C14:P14=평가!C30:P30))/SUMPRODUCT((평가!C14:P14&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="14" t="inlineStr">
@@ -3251,6 +3324,10 @@
         <f>IFERROR(SUMPRODUCT((평가!C15:P15&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")*(평가!C15:P15=평가!C29:P29))/SUMPRODUCT((평가!C15:P15&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")),"")</f>
         <v/>
       </c>
+      <c r="Z14" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C15:P15&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")*(평가!C15:P15=평가!C30:P30))/SUMPRODUCT((평가!C15:P15&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="14" t="inlineStr">
@@ -3354,6 +3431,10 @@
         <f>IFERROR(SUMPRODUCT((평가!C16:P16&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")*(평가!C16:P16=평가!C29:P29))/SUMPRODUCT((평가!C16:P16&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")),"")</f>
         <v/>
       </c>
+      <c r="Z15" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C16:P16&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")*(평가!C16:P16=평가!C30:P30))/SUMPRODUCT((평가!C16:P16&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="14" t="inlineStr">
@@ -3457,6 +3538,10 @@
         <f>IFERROR(SUMPRODUCT((평가!C17:P17&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")*(평가!C17:P17=평가!C29:P29))/SUMPRODUCT((평가!C17:P17&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")),"")</f>
         <v/>
       </c>
+      <c r="Z16" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C17:P17&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")*(평가!C17:P17=평가!C30:P30))/SUMPRODUCT((평가!C17:P17&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="14" t="inlineStr">
@@ -3560,6 +3645,10 @@
         <f>IFERROR(SUMPRODUCT((평가!C18:P18&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")*(평가!C18:P18=평가!C29:P29))/SUMPRODUCT((평가!C18:P18&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")),"")</f>
         <v/>
       </c>
+      <c r="Z17" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C18:P18&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")*(평가!C18:P18=평가!C30:P30))/SUMPRODUCT((평가!C18:P18&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="14" t="inlineStr">
@@ -3663,6 +3752,10 @@
         <f>IFERROR(SUMPRODUCT((평가!C19:P19&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")*(평가!C19:P19=평가!C29:P29))/SUMPRODUCT((평가!C19:P19&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")),"")</f>
         <v/>
       </c>
+      <c r="Z18" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C19:P19&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")*(평가!C19:P19=평가!C30:P30))/SUMPRODUCT((평가!C19:P19&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="14" t="inlineStr">
@@ -3766,6 +3859,10 @@
         <f>IFERROR(SUMPRODUCT((평가!C20:P20&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")*(평가!C20:P20=평가!C29:P29))/SUMPRODUCT((평가!C20:P20&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")),"")</f>
         <v/>
       </c>
+      <c r="Z19" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C20:P20&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")*(평가!C20:P20=평가!C30:P30))/SUMPRODUCT((평가!C20:P20&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="14" t="inlineStr">
@@ -3869,6 +3966,10 @@
         <f>IFERROR(SUMPRODUCT((평가!C21:P21&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")*(평가!C21:P21=평가!C29:P29))/SUMPRODUCT((평가!C21:P21&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")),"")</f>
         <v/>
       </c>
+      <c r="Z20" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C21:P21&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")*(평가!C21:P21=평가!C30:P30))/SUMPRODUCT((평가!C21:P21&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="14" t="inlineStr">
@@ -3972,6 +4073,10 @@
         <f>IFERROR(SUMPRODUCT((평가!C22:P22&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")*(평가!C22:P22=평가!C29:P29))/SUMPRODUCT((평가!C22:P22&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")),"")</f>
         <v/>
       </c>
+      <c r="Z21" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C22:P22&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")*(평가!C22:P22=평가!C30:P30))/SUMPRODUCT((평가!C22:P22&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="14" t="inlineStr">
@@ -4075,6 +4180,10 @@
         <f>IFERROR(SUMPRODUCT((평가!C23:P23&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")*(평가!C23:P23=평가!C29:P29))/SUMPRODUCT((평가!C23:P23&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")),"")</f>
         <v/>
       </c>
+      <c r="Z22" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C23:P23&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")*(평가!C23:P23=평가!C30:P30))/SUMPRODUCT((평가!C23:P23&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="14" t="inlineStr">
@@ -4178,6 +4287,10 @@
         <f>IFERROR(SUMPRODUCT((평가!C24:P24&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")*(평가!C24:P24=평가!C29:P29))/SUMPRODUCT((평가!C24:P24&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")),"")</f>
         <v/>
       </c>
+      <c r="Z23" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C24:P24&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")*(평가!C24:P24=평가!C30:P30))/SUMPRODUCT((평가!C24:P24&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="14" t="inlineStr">
@@ -4281,6 +4394,10 @@
         <f>IFERROR(SUMPRODUCT((평가!C25:P25&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")*(평가!C25:P25=평가!C29:P29))/SUMPRODUCT((평가!C25:P25&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")),"")</f>
         <v/>
       </c>
+      <c r="Z24" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C25:P25&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")*(평가!C25:P25=평가!C30:P30))/SUMPRODUCT((평가!C25:P25&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="14" t="inlineStr">
@@ -4384,6 +4501,10 @@
         <f>IFERROR(SUMPRODUCT((평가!C26:P26&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")*(평가!C26:P26=평가!C29:P29))/SUMPRODUCT((평가!C26:P26&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")),"")</f>
         <v/>
       </c>
+      <c r="Z25" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C26:P26&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")*(평가!C26:P26=평가!C30:P30))/SUMPRODUCT((평가!C26:P26&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="14" t="inlineStr">
@@ -4487,6 +4608,10 @@
         <f>IFERROR(SUMPRODUCT((평가!C27:P27&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")*(평가!C27:P27=평가!C29:P29))/SUMPRODUCT((평가!C27:P27&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")),"")</f>
         <v/>
       </c>
+      <c r="Z26" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C27:P27&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")*(평가!C27:P27=평가!C30:P30))/SUMPRODUCT((평가!C27:P27&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="14" t="inlineStr">
@@ -4590,6 +4715,10 @@
         <f>IFERROR(SUMPRODUCT((평가!C28:P28&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")*(평가!C28:P28=평가!C29:P29))/SUMPRODUCT((평가!C28:P28&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")),"")</f>
         <v/>
       </c>
+      <c r="Z27" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C28:P28&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")*(평가!C28:P28=평가!C30:P30))/SUMPRODUCT((평가!C28:P28&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="14" t="inlineStr">
@@ -4690,6 +4819,117 @@
         <v/>
       </c>
       <c r="Y28" s="18">
+        <f>"-"</f>
+        <v/>
+      </c>
+      <c r="Z28" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C29:P29&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")*(평가!C29:P29=평가!C30:P30))/SUMPRODUCT((평가!C29:P29&lt;&gt;"")*(평가!C30:P30&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="B29" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C6:P6&lt;&gt;"")*(평가!C30:P30=평가!C6:P6))/SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C6:P6&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+      <c r="C29" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C7:P7&lt;&gt;"")*(평가!C30:P30=평가!C7:P7))/SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C7:P7&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+      <c r="D29" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C8:P8&lt;&gt;"")*(평가!C30:P30=평가!C8:P8))/SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C8:P8&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C9:P9&lt;&gt;"")*(평가!C30:P30=평가!C9:P9))/SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C9:P9&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C10:P10&lt;&gt;"")*(평가!C30:P30=평가!C10:P10))/SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C10:P10&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C11:P11&lt;&gt;"")*(평가!C30:P30=평가!C11:P11))/SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C11:P11&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C12:P12&lt;&gt;"")*(평가!C30:P30=평가!C12:P12))/SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C12:P12&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+      <c r="I29" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C13:P13&lt;&gt;"")*(평가!C30:P30=평가!C13:P13))/SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C13:P13&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+      <c r="J29" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C14:P14&lt;&gt;"")*(평가!C30:P30=평가!C14:P14))/SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C14:P14&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+      <c r="K29" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C15:P15&lt;&gt;"")*(평가!C30:P30=평가!C15:P15))/SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C15:P15&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+      <c r="L29" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C16:P16&lt;&gt;"")*(평가!C30:P30=평가!C16:P16))/SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C16:P16&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+      <c r="M29" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C17:P17&lt;&gt;"")*(평가!C30:P30=평가!C17:P17))/SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C17:P17&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+      <c r="N29" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C18:P18&lt;&gt;"")*(평가!C30:P30=평가!C18:P18))/SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C18:P18&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+      <c r="O29" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C19:P19&lt;&gt;"")*(평가!C30:P30=평가!C19:P19))/SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C19:P19&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+      <c r="P29" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C20:P20&lt;&gt;"")*(평가!C30:P30=평가!C20:P20))/SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C20:P20&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+      <c r="Q29" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C21:P21&lt;&gt;"")*(평가!C30:P30=평가!C21:P21))/SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C21:P21&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+      <c r="R29" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C22:P22&lt;&gt;"")*(평가!C30:P30=평가!C22:P22))/SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C22:P22&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+      <c r="S29" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C23:P23&lt;&gt;"")*(평가!C30:P30=평가!C23:P23))/SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C23:P23&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+      <c r="T29" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C24:P24&lt;&gt;"")*(평가!C30:P30=평가!C24:P24))/SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C24:P24&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+      <c r="U29" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C25:P25&lt;&gt;"")*(평가!C30:P30=평가!C25:P25))/SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C25:P25&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+      <c r="V29" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C26:P26&lt;&gt;"")*(평가!C30:P30=평가!C26:P26))/SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C26:P26&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+      <c r="W29" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C27:P27&lt;&gt;"")*(평가!C30:P30=평가!C27:P27))/SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C27:P27&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+      <c r="X29" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C28:P28&lt;&gt;"")*(평가!C30:P30=평가!C28:P28))/SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C28:P28&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+      <c r="Y29" s="19">
+        <f>IFERROR(SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")*(평가!C30:P30=평가!C29:P29))/SUMPRODUCT((평가!C30:P30&lt;&gt;"")*(평가!C29:P29&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+      <c r="Z29" s="19">
         <f>"-"</f>
         <v/>
       </c>
@@ -4709,7 +4949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5231,6 +5471,26 @@
       <c r="D28" s="16" t="inlineStr">
         <is>
           <t>순수 화학 연구, 화학 이론</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>공학</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>자동차 설계, 동력·구동 시스템</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M279"/>
+  <dimension ref="A1:M303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -15836,6 +16096,798 @@
       <c r="L279" s="46" t="n"/>
       <c r="M279" s="46" t="n"/>
     </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>277</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>건축학과</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>6</v>
+      </c>
+      <c r="E280" t="n">
+        <v>30</v>
+      </c>
+      <c r="F280" s="48">
+        <f>SUMPRODUCT(('평가'!C6:P6&lt;&gt;"")*('평가'!C30:P30&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G280" s="48">
+        <f>SUMPRODUCT(('평가'!C6:P6&lt;&gt;"")*('평가'!C30:P30&lt;&gt;"")*('평가'!C6:P6='평가'!C30:P30))</f>
+        <v/>
+      </c>
+      <c r="H280" s="49">
+        <f>IF(F280=0,"",G280/F280)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>278</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>국어국문학과</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>7</v>
+      </c>
+      <c r="E281" t="n">
+        <v>30</v>
+      </c>
+      <c r="F281" s="48">
+        <f>SUMPRODUCT(('평가'!C7:P7&lt;&gt;"")*('평가'!C30:P30&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G281" s="48">
+        <f>SUMPRODUCT(('평가'!C7:P7&lt;&gt;"")*('평가'!C30:P30&lt;&gt;"")*('평가'!C7:P7='평가'!C30:P30))</f>
+        <v/>
+      </c>
+      <c r="H281" s="49">
+        <f>IF(F281=0,"",G281/F281)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>279</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>심리학과</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>8</v>
+      </c>
+      <c r="E282" t="n">
+        <v>30</v>
+      </c>
+      <c r="F282" s="48">
+        <f>SUMPRODUCT(('평가'!C8:P8&lt;&gt;"")*('평가'!C30:P30&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G282" s="48">
+        <f>SUMPRODUCT(('평가'!C8:P8&lt;&gt;"")*('평가'!C30:P30&lt;&gt;"")*('평가'!C8:P8='평가'!C30:P30))</f>
+        <v/>
+      </c>
+      <c r="H282" s="49">
+        <f>IF(F282=0,"",G282/F282)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>280</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>기계공학과</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>9</v>
+      </c>
+      <c r="E283" t="n">
+        <v>30</v>
+      </c>
+      <c r="F283" s="48">
+        <f>SUMPRODUCT(('평가'!C9:P9&lt;&gt;"")*('평가'!C30:P30&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G283" s="48">
+        <f>SUMPRODUCT(('평가'!C9:P9&lt;&gt;"")*('평가'!C30:P30&lt;&gt;"")*('평가'!C9:P9='평가'!C30:P30))</f>
+        <v/>
+      </c>
+      <c r="H283" s="49">
+        <f>IF(F283=0,"",G283/F283)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>281</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>화학과</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="D284" t="n">
+        <v>10</v>
+      </c>
+      <c r="E284" t="n">
+        <v>30</v>
+      </c>
+      <c r="F284" s="48">
+        <f>SUMPRODUCT(('평가'!C10:P10&lt;&gt;"")*('평가'!C30:P30&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G284" s="48">
+        <f>SUMPRODUCT(('평가'!C10:P10&lt;&gt;"")*('평가'!C30:P30&lt;&gt;"")*('평가'!C10:P10='평가'!C30:P30))</f>
+        <v/>
+      </c>
+      <c r="H284" s="49">
+        <f>IF(F284=0,"",G284/F284)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>282</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>산업공학과</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="D285" t="n">
+        <v>11</v>
+      </c>
+      <c r="E285" t="n">
+        <v>30</v>
+      </c>
+      <c r="F285" s="48">
+        <f>SUMPRODUCT(('평가'!C11:P11&lt;&gt;"")*('평가'!C30:P30&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G285" s="48">
+        <f>SUMPRODUCT(('평가'!C11:P11&lt;&gt;"")*('평가'!C30:P30&lt;&gt;"")*('평가'!C11:P11='평가'!C30:P30))</f>
+        <v/>
+      </c>
+      <c r="H285" s="49">
+        <f>IF(F285=0,"",G285/F285)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>283</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>신소재공학과</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="D286" t="n">
+        <v>12</v>
+      </c>
+      <c r="E286" t="n">
+        <v>30</v>
+      </c>
+      <c r="F286" s="48">
+        <f>SUMPRODUCT(('평가'!C12:P12&lt;&gt;"")*('평가'!C30:P30&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G286" s="48">
+        <f>SUMPRODUCT(('평가'!C12:P12&lt;&gt;"")*('평가'!C30:P30&lt;&gt;"")*('평가'!C12:P12='평가'!C30:P30))</f>
+        <v/>
+      </c>
+      <c r="H286" s="49">
+        <f>IF(F286=0,"",G286/F286)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>284</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>조선해양공학과</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="D287" t="n">
+        <v>13</v>
+      </c>
+      <c r="E287" t="n">
+        <v>30</v>
+      </c>
+      <c r="F287" s="48">
+        <f>SUMPRODUCT(('평가'!C13:P13&lt;&gt;"")*('평가'!C30:P30&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G287" s="48">
+        <f>SUMPRODUCT(('평가'!C13:P13&lt;&gt;"")*('평가'!C30:P30&lt;&gt;"")*('평가'!C13:P13='평가'!C30:P30))</f>
+        <v/>
+      </c>
+      <c r="H287" s="49">
+        <f>IF(F287=0,"",G287/F287)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>285</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>의예과</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="D288" t="n">
+        <v>14</v>
+      </c>
+      <c r="E288" t="n">
+        <v>30</v>
+      </c>
+      <c r="F288" s="48">
+        <f>SUMPRODUCT(('평가'!C14:P14&lt;&gt;"")*('평가'!C30:P30&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G288" s="48">
+        <f>SUMPRODUCT(('평가'!C14:P14&lt;&gt;"")*('평가'!C30:P30&lt;&gt;"")*('평가'!C14:P14='평가'!C30:P30))</f>
+        <v/>
+      </c>
+      <c r="H288" s="49">
+        <f>IF(F288=0,"",G288/F288)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>286</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>수학과</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="D289" t="n">
+        <v>15</v>
+      </c>
+      <c r="E289" t="n">
+        <v>30</v>
+      </c>
+      <c r="F289" s="48">
+        <f>SUMPRODUCT(('평가'!C15:P15&lt;&gt;"")*('평가'!C30:P30&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G289" s="48">
+        <f>SUMPRODUCT(('평가'!C15:P15&lt;&gt;"")*('평가'!C30:P30&lt;&gt;"")*('평가'!C15:P15='평가'!C30:P30))</f>
+        <v/>
+      </c>
+      <c r="H289" s="49">
+        <f>IF(F289=0,"",G289/F289)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>287</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>경영학과</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>16</v>
+      </c>
+      <c r="E290" t="n">
+        <v>30</v>
+      </c>
+      <c r="F290" s="48">
+        <f>SUMPRODUCT(('평가'!C16:P16&lt;&gt;"")*('평가'!C30:P30&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G290" s="48">
+        <f>SUMPRODUCT(('평가'!C16:P16&lt;&gt;"")*('평가'!C30:P30&lt;&gt;"")*('평가'!C16:P16='평가'!C30:P30))</f>
+        <v/>
+      </c>
+      <c r="H290" s="49">
+        <f>IF(F290=0,"",G290/F290)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>288</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>약학과</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
+        <v>17</v>
+      </c>
+      <c r="E291" t="n">
+        <v>30</v>
+      </c>
+      <c r="F291" s="48">
+        <f>SUMPRODUCT(('평가'!C17:P17&lt;&gt;"")*('평가'!C30:P30&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G291" s="48">
+        <f>SUMPRODUCT(('평가'!C17:P17&lt;&gt;"")*('평가'!C30:P30&lt;&gt;"")*('평가'!C17:P17='평가'!C30:P30))</f>
+        <v/>
+      </c>
+      <c r="H291" s="49">
+        <f>IF(F291=0,"",G291/F291)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>289</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>사회학과</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="D292" t="n">
+        <v>18</v>
+      </c>
+      <c r="E292" t="n">
+        <v>30</v>
+      </c>
+      <c r="F292" s="48">
+        <f>SUMPRODUCT(('평가'!C18:P18&lt;&gt;"")*('평가'!C30:P30&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G292" s="48">
+        <f>SUMPRODUCT(('평가'!C18:P18&lt;&gt;"")*('평가'!C30:P30&lt;&gt;"")*('평가'!C18:P18='평가'!C30:P30))</f>
+        <v/>
+      </c>
+      <c r="H292" s="49">
+        <f>IF(F292=0,"",G292/F292)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>290</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>경제학과</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>19</v>
+      </c>
+      <c r="E293" t="n">
+        <v>30</v>
+      </c>
+      <c r="F293" s="48">
+        <f>SUMPRODUCT(('평가'!C19:P19&lt;&gt;"")*('평가'!C30:P30&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G293" s="48">
+        <f>SUMPRODUCT(('평가'!C19:P19&lt;&gt;"")*('평가'!C30:P30&lt;&gt;"")*('평가'!C19:P19='평가'!C30:P30))</f>
+        <v/>
+      </c>
+      <c r="H293" s="49">
+        <f>IF(F293=0,"",G293/F293)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>291</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>생명과학과</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="D294" t="n">
+        <v>20</v>
+      </c>
+      <c r="E294" t="n">
+        <v>30</v>
+      </c>
+      <c r="F294" s="48">
+        <f>SUMPRODUCT(('평가'!C20:P20&lt;&gt;"")*('평가'!C30:P30&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G294" s="48">
+        <f>SUMPRODUCT(('평가'!C20:P20&lt;&gt;"")*('평가'!C30:P30&lt;&gt;"")*('평가'!C20:P20='평가'!C30:P30))</f>
+        <v/>
+      </c>
+      <c r="H294" s="49">
+        <f>IF(F294=0,"",G294/F294)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>292</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>미디어커뮤니케이션학과</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="D295" t="n">
+        <v>21</v>
+      </c>
+      <c r="E295" t="n">
+        <v>30</v>
+      </c>
+      <c r="F295" s="48">
+        <f>SUMPRODUCT(('평가'!C21:P21&lt;&gt;"")*('평가'!C30:P30&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G295" s="48">
+        <f>SUMPRODUCT(('평가'!C21:P21&lt;&gt;"")*('평가'!C30:P30&lt;&gt;"")*('평가'!C21:P21='평가'!C30:P30))</f>
+        <v/>
+      </c>
+      <c r="H295" s="49">
+        <f>IF(F295=0,"",G295/F295)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>293</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>화학공학과</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="D296" t="n">
+        <v>22</v>
+      </c>
+      <c r="E296" t="n">
+        <v>30</v>
+      </c>
+      <c r="F296" s="48">
+        <f>SUMPRODUCT(('평가'!C22:P22&lt;&gt;"")*('평가'!C30:P30&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G296" s="48">
+        <f>SUMPRODUCT(('평가'!C22:P22&lt;&gt;"")*('평가'!C30:P30&lt;&gt;"")*('평가'!C22:P22='평가'!C30:P30))</f>
+        <v/>
+      </c>
+      <c r="H296" s="49">
+        <f>IF(F296=0,"",G296/F296)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>294</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>디자인학과</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="D297" t="n">
+        <v>23</v>
+      </c>
+      <c r="E297" t="n">
+        <v>30</v>
+      </c>
+      <c r="F297" s="48">
+        <f>SUMPRODUCT(('평가'!C23:P23&lt;&gt;"")*('평가'!C30:P30&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G297" s="48">
+        <f>SUMPRODUCT(('평가'!C23:P23&lt;&gt;"")*('평가'!C30:P30&lt;&gt;"")*('평가'!C23:P23='평가'!C30:P30))</f>
+        <v/>
+      </c>
+      <c r="H297" s="49">
+        <f>IF(F297=0,"",G297/F297)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>295</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>식품영양학과</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="D298" t="n">
+        <v>24</v>
+      </c>
+      <c r="E298" t="n">
+        <v>30</v>
+      </c>
+      <c r="F298" s="48">
+        <f>SUMPRODUCT(('평가'!C24:P24&lt;&gt;"")*('평가'!C30:P30&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G298" s="48">
+        <f>SUMPRODUCT(('평가'!C24:P24&lt;&gt;"")*('평가'!C30:P30&lt;&gt;"")*('평가'!C24:P24='평가'!C30:P30))</f>
+        <v/>
+      </c>
+      <c r="H298" s="49">
+        <f>IF(F298=0,"",G298/F298)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>296</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>간호학과</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="D299" t="n">
+        <v>25</v>
+      </c>
+      <c r="E299" t="n">
+        <v>30</v>
+      </c>
+      <c r="F299" s="48">
+        <f>SUMPRODUCT(('평가'!C25:P25&lt;&gt;"")*('평가'!C30:P30&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G299" s="48">
+        <f>SUMPRODUCT(('평가'!C25:P25&lt;&gt;"")*('평가'!C30:P30&lt;&gt;"")*('평가'!C25:P25='평가'!C30:P30))</f>
+        <v/>
+      </c>
+      <c r="H299" s="49">
+        <f>IF(F299=0,"",G299/F299)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>297</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>전기전자공학과</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="D300" t="n">
+        <v>26</v>
+      </c>
+      <c r="E300" t="n">
+        <v>30</v>
+      </c>
+      <c r="F300" s="48">
+        <f>SUMPRODUCT(('평가'!C26:P26&lt;&gt;"")*('평가'!C30:P30&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G300" s="48">
+        <f>SUMPRODUCT(('평가'!C26:P26&lt;&gt;"")*('평가'!C30:P30&lt;&gt;"")*('평가'!C26:P26='평가'!C30:P30))</f>
+        <v/>
+      </c>
+      <c r="H300" s="49">
+        <f>IF(F300=0,"",G300/F300)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>298</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>사학과</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="D301" t="n">
+        <v>27</v>
+      </c>
+      <c r="E301" t="n">
+        <v>30</v>
+      </c>
+      <c r="F301" s="48">
+        <f>SUMPRODUCT(('평가'!C27:P27&lt;&gt;"")*('평가'!C30:P30&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G301" s="48">
+        <f>SUMPRODUCT(('평가'!C27:P27&lt;&gt;"")*('평가'!C30:P30&lt;&gt;"")*('평가'!C27:P27='평가'!C30:P30))</f>
+        <v/>
+      </c>
+      <c r="H301" s="49">
+        <f>IF(F301=0,"",G301/F301)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>299</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>응용통계학과</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="D302" t="n">
+        <v>28</v>
+      </c>
+      <c r="E302" t="n">
+        <v>30</v>
+      </c>
+      <c r="F302" s="48">
+        <f>SUMPRODUCT(('평가'!C28:P28&lt;&gt;"")*('평가'!C30:P30&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G302" s="48">
+        <f>SUMPRODUCT(('평가'!C28:P28&lt;&gt;"")*('평가'!C30:P30&lt;&gt;"")*('평가'!C28:P28='평가'!C30:P30))</f>
+        <v/>
+      </c>
+      <c r="H302" s="49">
+        <f>IF(F302=0,"",G302/F302)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>300</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>컴퓨터공학과</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>자동차공학과</t>
+        </is>
+      </c>
+      <c r="D303" t="n">
+        <v>29</v>
+      </c>
+      <c r="E303" t="n">
+        <v>30</v>
+      </c>
+      <c r="F303" s="48">
+        <f>SUMPRODUCT(('평가'!C29:P29&lt;&gt;"")*('평가'!C30:P30&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="G303" s="48">
+        <f>SUMPRODUCT(('평가'!C29:P29&lt;&gt;"")*('평가'!C30:P30&lt;&gt;"")*('평가'!C29:P29='평가'!C30:P30))</f>
+        <v/>
+      </c>
+      <c r="H303" s="49">
+        <f>IF(F303=0,"",G303/F303)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A3:M279"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15848,7 +16900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15880,6 +16932,7 @@
     <col width="9" customWidth="1" min="27" max="27"/>
     <col width="9" customWidth="1" min="28" max="28"/>
     <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16028,6 +17081,11 @@
           <t>Group 24</t>
         </is>
       </c>
+      <c r="AD1" s="45" t="inlineStr">
+        <is>
+          <t>Group 25</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="46" t="inlineStr">
@@ -16036,115 +17094,119 @@
         </is>
       </c>
       <c r="B2" s="46">
-        <f>COUNT('평가'!C6:C29)</f>
+        <f>COUNT('평가'!C6:C30)</f>
         <v/>
       </c>
       <c r="C2" s="46">
-        <f>COUNTIF(F2:AC2,"&gt;0")</f>
+        <f>COUNTIF(F2:AD2,"&gt;0")</f>
         <v/>
       </c>
       <c r="D2" s="46">
-        <f>MAX(F2:AC2)</f>
+        <f>MAX(F2:AD2)</f>
         <v/>
       </c>
       <c r="E2" s="46">
-        <f>IF(B2=0,"no response yet",IF(B2&lt;24,"missing depts",IF(C2=1,"all one group?",IF(C2&gt;18,"too many groups?","OK"))))</f>
+        <f>IF(B2=0,"no response yet",IF(B2&lt;25,"missing depts",IF(C2=1,"all one group?",IF(C2&gt;18,"too many groups?","OK"))))</f>
         <v/>
       </c>
       <c r="F2" s="47">
-        <f>COUNTIF('평가'!$C$6:$C$29,1)</f>
+        <f>COUNTIF('평가'!$C$6:$C$30,1)</f>
         <v/>
       </c>
       <c r="G2" s="47">
-        <f>COUNTIF('평가'!$C$6:$C$29,2)</f>
+        <f>COUNTIF('평가'!$C$6:$C$30,2)</f>
         <v/>
       </c>
       <c r="H2" s="47">
-        <f>COUNTIF('평가'!$C$6:$C$29,3)</f>
+        <f>COUNTIF('평가'!$C$6:$C$30,3)</f>
         <v/>
       </c>
       <c r="I2" s="47">
-        <f>COUNTIF('평가'!$C$6:$C$29,4)</f>
+        <f>COUNTIF('평가'!$C$6:$C$30,4)</f>
         <v/>
       </c>
       <c r="J2" s="47">
-        <f>COUNTIF('평가'!$C$6:$C$29,5)</f>
+        <f>COUNTIF('평가'!$C$6:$C$30,5)</f>
         <v/>
       </c>
       <c r="K2" s="47">
-        <f>COUNTIF('평가'!$C$6:$C$29,6)</f>
+        <f>COUNTIF('평가'!$C$6:$C$30,6)</f>
         <v/>
       </c>
       <c r="L2" s="47">
-        <f>COUNTIF('평가'!$C$6:$C$29,7)</f>
+        <f>COUNTIF('평가'!$C$6:$C$30,7)</f>
         <v/>
       </c>
       <c r="M2" s="47">
-        <f>COUNTIF('평가'!$C$6:$C$29,8)</f>
+        <f>COUNTIF('평가'!$C$6:$C$30,8)</f>
         <v/>
       </c>
       <c r="N2" s="47">
-        <f>COUNTIF('평가'!$C$6:$C$29,9)</f>
+        <f>COUNTIF('평가'!$C$6:$C$30,9)</f>
         <v/>
       </c>
       <c r="O2" s="47">
-        <f>COUNTIF('평가'!$C$6:$C$29,10)</f>
+        <f>COUNTIF('평가'!$C$6:$C$30,10)</f>
         <v/>
       </c>
       <c r="P2" s="47">
-        <f>COUNTIF('평가'!$C$6:$C$29,11)</f>
+        <f>COUNTIF('평가'!$C$6:$C$30,11)</f>
         <v/>
       </c>
       <c r="Q2" s="47">
-        <f>COUNTIF('평가'!$C$6:$C$29,12)</f>
+        <f>COUNTIF('평가'!$C$6:$C$30,12)</f>
         <v/>
       </c>
       <c r="R2" s="47">
-        <f>COUNTIF('평가'!$C$6:$C$29,13)</f>
+        <f>COUNTIF('평가'!$C$6:$C$30,13)</f>
         <v/>
       </c>
       <c r="S2" s="47">
-        <f>COUNTIF('평가'!$C$6:$C$29,14)</f>
+        <f>COUNTIF('평가'!$C$6:$C$30,14)</f>
         <v/>
       </c>
       <c r="T2" s="47">
-        <f>COUNTIF('평가'!$C$6:$C$29,15)</f>
+        <f>COUNTIF('평가'!$C$6:$C$30,15)</f>
         <v/>
       </c>
       <c r="U2" s="47">
-        <f>COUNTIF('평가'!$C$6:$C$29,16)</f>
+        <f>COUNTIF('평가'!$C$6:$C$30,16)</f>
         <v/>
       </c>
       <c r="V2" s="47">
-        <f>COUNTIF('평가'!$C$6:$C$29,17)</f>
+        <f>COUNTIF('평가'!$C$6:$C$30,17)</f>
         <v/>
       </c>
       <c r="W2" s="47">
-        <f>COUNTIF('평가'!$C$6:$C$29,18)</f>
+        <f>COUNTIF('평가'!$C$6:$C$30,18)</f>
         <v/>
       </c>
       <c r="X2" s="47">
-        <f>COUNTIF('평가'!$C$6:$C$29,19)</f>
+        <f>COUNTIF('평가'!$C$6:$C$30,19)</f>
         <v/>
       </c>
       <c r="Y2" s="47">
-        <f>COUNTIF('평가'!$C$6:$C$29,20)</f>
+        <f>COUNTIF('평가'!$C$6:$C$30,20)</f>
         <v/>
       </c>
       <c r="Z2" s="47">
-        <f>COUNTIF('평가'!$C$6:$C$29,21)</f>
+        <f>COUNTIF('평가'!$C$6:$C$30,21)</f>
         <v/>
       </c>
       <c r="AA2" s="47">
-        <f>COUNTIF('평가'!$C$6:$C$29,22)</f>
+        <f>COUNTIF('평가'!$C$6:$C$30,22)</f>
         <v/>
       </c>
       <c r="AB2" s="47">
-        <f>COUNTIF('평가'!$C$6:$C$29,23)</f>
+        <f>COUNTIF('평가'!$C$6:$C$30,23)</f>
         <v/>
       </c>
       <c r="AC2" s="47">
-        <f>COUNTIF('평가'!$C$6:$C$29,24)</f>
+        <f>COUNTIF('평가'!$C$6:$C$30,24)</f>
+        <v/>
+      </c>
+      <c r="AD2" s="47">
+        <f>COUNTIF('평가'!$C$6:$C$30,25)</f>
         <v/>
       </c>
     </row>
@@ -16155,115 +17217,119 @@
         </is>
       </c>
       <c r="B3" s="46">
-        <f>COUNT('평가'!D6:D29)</f>
+        <f>COUNT('평가'!D6:D30)</f>
         <v/>
       </c>
       <c r="C3" s="46">
-        <f>COUNTIF(F3:AC3,"&gt;0")</f>
+        <f>COUNTIF(F3:AD3,"&gt;0")</f>
         <v/>
       </c>
       <c r="D3" s="46">
-        <f>MAX(F3:AC3)</f>
+        <f>MAX(F3:AD3)</f>
         <v/>
       </c>
       <c r="E3" s="46">
-        <f>IF(B3=0,"no response yet",IF(B3&lt;24,"missing depts",IF(C3=1,"all one group?",IF(C3&gt;18,"too many groups?","OK"))))</f>
+        <f>IF(B3=0,"no response yet",IF(B3&lt;25,"missing depts",IF(C3=1,"all one group?",IF(C3&gt;18,"too many groups?","OK"))))</f>
         <v/>
       </c>
       <c r="F3" s="47">
-        <f>COUNTIF('평가'!$D$6:$D$29,1)</f>
+        <f>COUNTIF('평가'!$D$6:$D$30,1)</f>
         <v/>
       </c>
       <c r="G3" s="47">
-        <f>COUNTIF('평가'!$D$6:$D$29,2)</f>
+        <f>COUNTIF('평가'!$D$6:$D$30,2)</f>
         <v/>
       </c>
       <c r="H3" s="47">
-        <f>COUNTIF('평가'!$D$6:$D$29,3)</f>
+        <f>COUNTIF('평가'!$D$6:$D$30,3)</f>
         <v/>
       </c>
       <c r="I3" s="47">
-        <f>COUNTIF('평가'!$D$6:$D$29,4)</f>
+        <f>COUNTIF('평가'!$D$6:$D$30,4)</f>
         <v/>
       </c>
       <c r="J3" s="47">
-        <f>COUNTIF('평가'!$D$6:$D$29,5)</f>
+        <f>COUNTIF('평가'!$D$6:$D$30,5)</f>
         <v/>
       </c>
       <c r="K3" s="47">
-        <f>COUNTIF('평가'!$D$6:$D$29,6)</f>
+        <f>COUNTIF('평가'!$D$6:$D$30,6)</f>
         <v/>
       </c>
       <c r="L3" s="47">
-        <f>COUNTIF('평가'!$D$6:$D$29,7)</f>
+        <f>COUNTIF('평가'!$D$6:$D$30,7)</f>
         <v/>
       </c>
       <c r="M3" s="47">
-        <f>COUNTIF('평가'!$D$6:$D$29,8)</f>
+        <f>COUNTIF('평가'!$D$6:$D$30,8)</f>
         <v/>
       </c>
       <c r="N3" s="47">
-        <f>COUNTIF('평가'!$D$6:$D$29,9)</f>
+        <f>COUNTIF('평가'!$D$6:$D$30,9)</f>
         <v/>
       </c>
       <c r="O3" s="47">
-        <f>COUNTIF('평가'!$D$6:$D$29,10)</f>
+        <f>COUNTIF('평가'!$D$6:$D$30,10)</f>
         <v/>
       </c>
       <c r="P3" s="47">
-        <f>COUNTIF('평가'!$D$6:$D$29,11)</f>
+        <f>COUNTIF('평가'!$D$6:$D$30,11)</f>
         <v/>
       </c>
       <c r="Q3" s="47">
-        <f>COUNTIF('평가'!$D$6:$D$29,12)</f>
+        <f>COUNTIF('평가'!$D$6:$D$30,12)</f>
         <v/>
       </c>
       <c r="R3" s="47">
-        <f>COUNTIF('평가'!$D$6:$D$29,13)</f>
+        <f>COUNTIF('평가'!$D$6:$D$30,13)</f>
         <v/>
       </c>
       <c r="S3" s="47">
-        <f>COUNTIF('평가'!$D$6:$D$29,14)</f>
+        <f>COUNTIF('평가'!$D$6:$D$30,14)</f>
         <v/>
       </c>
       <c r="T3" s="47">
-        <f>COUNTIF('평가'!$D$6:$D$29,15)</f>
+        <f>COUNTIF('평가'!$D$6:$D$30,15)</f>
         <v/>
       </c>
       <c r="U3" s="47">
-        <f>COUNTIF('평가'!$D$6:$D$29,16)</f>
+        <f>COUNTIF('평가'!$D$6:$D$30,16)</f>
         <v/>
       </c>
       <c r="V3" s="47">
-        <f>COUNTIF('평가'!$D$6:$D$29,17)</f>
+        <f>COUNTIF('평가'!$D$6:$D$30,17)</f>
         <v/>
       </c>
       <c r="W3" s="47">
-        <f>COUNTIF('평가'!$D$6:$D$29,18)</f>
+        <f>COUNTIF('평가'!$D$6:$D$30,18)</f>
         <v/>
       </c>
       <c r="X3" s="47">
-        <f>COUNTIF('평가'!$D$6:$D$29,19)</f>
+        <f>COUNTIF('평가'!$D$6:$D$30,19)</f>
         <v/>
       </c>
       <c r="Y3" s="47">
-        <f>COUNTIF('평가'!$D$6:$D$29,20)</f>
+        <f>COUNTIF('평가'!$D$6:$D$30,20)</f>
         <v/>
       </c>
       <c r="Z3" s="47">
-        <f>COUNTIF('평가'!$D$6:$D$29,21)</f>
+        <f>COUNTIF('평가'!$D$6:$D$30,21)</f>
         <v/>
       </c>
       <c r="AA3" s="47">
-        <f>COUNTIF('평가'!$D$6:$D$29,22)</f>
+        <f>COUNTIF('평가'!$D$6:$D$30,22)</f>
         <v/>
       </c>
       <c r="AB3" s="47">
-        <f>COUNTIF('평가'!$D$6:$D$29,23)</f>
+        <f>COUNTIF('평가'!$D$6:$D$30,23)</f>
         <v/>
       </c>
       <c r="AC3" s="47">
-        <f>COUNTIF('평가'!$D$6:$D$29,24)</f>
+        <f>COUNTIF('평가'!$D$6:$D$30,24)</f>
+        <v/>
+      </c>
+      <c r="AD3" s="47">
+        <f>COUNTIF('평가'!$D$6:$D$30,25)</f>
         <v/>
       </c>
     </row>
@@ -16274,115 +17340,119 @@
         </is>
       </c>
       <c r="B4" s="46">
-        <f>COUNT('평가'!E6:E29)</f>
+        <f>COUNT('평가'!E6:E30)</f>
         <v/>
       </c>
       <c r="C4" s="46">
-        <f>COUNTIF(F4:AC4,"&gt;0")</f>
+        <f>COUNTIF(F4:AD4,"&gt;0")</f>
         <v/>
       </c>
       <c r="D4" s="46">
-        <f>MAX(F4:AC4)</f>
+        <f>MAX(F4:AD4)</f>
         <v/>
       </c>
       <c r="E4" s="46">
-        <f>IF(B4=0,"no response yet",IF(B4&lt;24,"missing depts",IF(C4=1,"all one group?",IF(C4&gt;18,"too many groups?","OK"))))</f>
+        <f>IF(B4=0,"no response yet",IF(B4&lt;25,"missing depts",IF(C4=1,"all one group?",IF(C4&gt;18,"too many groups?","OK"))))</f>
         <v/>
       </c>
       <c r="F4" s="47">
-        <f>COUNTIF('평가'!$E$6:$E$29,1)</f>
+        <f>COUNTIF('평가'!$E$6:$E$30,1)</f>
         <v/>
       </c>
       <c r="G4" s="47">
-        <f>COUNTIF('평가'!$E$6:$E$29,2)</f>
+        <f>COUNTIF('평가'!$E$6:$E$30,2)</f>
         <v/>
       </c>
       <c r="H4" s="47">
-        <f>COUNTIF('평가'!$E$6:$E$29,3)</f>
+        <f>COUNTIF('평가'!$E$6:$E$30,3)</f>
         <v/>
       </c>
       <c r="I4" s="47">
-        <f>COUNTIF('평가'!$E$6:$E$29,4)</f>
+        <f>COUNTIF('평가'!$E$6:$E$30,4)</f>
         <v/>
       </c>
       <c r="J4" s="47">
-        <f>COUNTIF('평가'!$E$6:$E$29,5)</f>
+        <f>COUNTIF('평가'!$E$6:$E$30,5)</f>
         <v/>
       </c>
       <c r="K4" s="47">
-        <f>COUNTIF('평가'!$E$6:$E$29,6)</f>
+        <f>COUNTIF('평가'!$E$6:$E$30,6)</f>
         <v/>
       </c>
       <c r="L4" s="47">
-        <f>COUNTIF('평가'!$E$6:$E$29,7)</f>
+        <f>COUNTIF('평가'!$E$6:$E$30,7)</f>
         <v/>
       </c>
       <c r="M4" s="47">
-        <f>COUNTIF('평가'!$E$6:$E$29,8)</f>
+        <f>COUNTIF('평가'!$E$6:$E$30,8)</f>
         <v/>
       </c>
       <c r="N4" s="47">
-        <f>COUNTIF('평가'!$E$6:$E$29,9)</f>
+        <f>COUNTIF('평가'!$E$6:$E$30,9)</f>
         <v/>
       </c>
       <c r="O4" s="47">
-        <f>COUNTIF('평가'!$E$6:$E$29,10)</f>
+        <f>COUNTIF('평가'!$E$6:$E$30,10)</f>
         <v/>
       </c>
       <c r="P4" s="47">
-        <f>COUNTIF('평가'!$E$6:$E$29,11)</f>
+        <f>COUNTIF('평가'!$E$6:$E$30,11)</f>
         <v/>
       </c>
       <c r="Q4" s="47">
-        <f>COUNTIF('평가'!$E$6:$E$29,12)</f>
+        <f>COUNTIF('평가'!$E$6:$E$30,12)</f>
         <v/>
       </c>
       <c r="R4" s="47">
-        <f>COUNTIF('평가'!$E$6:$E$29,13)</f>
+        <f>COUNTIF('평가'!$E$6:$E$30,13)</f>
         <v/>
       </c>
       <c r="S4" s="47">
-        <f>COUNTIF('평가'!$E$6:$E$29,14)</f>
+        <f>COUNTIF('평가'!$E$6:$E$30,14)</f>
         <v/>
       </c>
       <c r="T4" s="47">
-        <f>COUNTIF('평가'!$E$6:$E$29,15)</f>
+        <f>COUNTIF('평가'!$E$6:$E$30,15)</f>
         <v/>
       </c>
       <c r="U4" s="47">
-        <f>COUNTIF('평가'!$E$6:$E$29,16)</f>
+        <f>COUNTIF('평가'!$E$6:$E$30,16)</f>
         <v/>
       </c>
       <c r="V4" s="47">
-        <f>COUNTIF('평가'!$E$6:$E$29,17)</f>
+        <f>COUNTIF('평가'!$E$6:$E$30,17)</f>
         <v/>
       </c>
       <c r="W4" s="47">
-        <f>COUNTIF('평가'!$E$6:$E$29,18)</f>
+        <f>COUNTIF('평가'!$E$6:$E$30,18)</f>
         <v/>
       </c>
       <c r="X4" s="47">
-        <f>COUNTIF('평가'!$E$6:$E$29,19)</f>
+        <f>COUNTIF('평가'!$E$6:$E$30,19)</f>
         <v/>
       </c>
       <c r="Y4" s="47">
-        <f>COUNTIF('평가'!$E$6:$E$29,20)</f>
+        <f>COUNTIF('평가'!$E$6:$E$30,20)</f>
         <v/>
       </c>
       <c r="Z4" s="47">
-        <f>COUNTIF('평가'!$E$6:$E$29,21)</f>
+        <f>COUNTIF('평가'!$E$6:$E$30,21)</f>
         <v/>
       </c>
       <c r="AA4" s="47">
-        <f>COUNTIF('평가'!$E$6:$E$29,22)</f>
+        <f>COUNTIF('평가'!$E$6:$E$30,22)</f>
         <v/>
       </c>
       <c r="AB4" s="47">
-        <f>COUNTIF('평가'!$E$6:$E$29,23)</f>
+        <f>COUNTIF('평가'!$E$6:$E$30,23)</f>
         <v/>
       </c>
       <c r="AC4" s="47">
-        <f>COUNTIF('평가'!$E$6:$E$29,24)</f>
+        <f>COUNTIF('평가'!$E$6:$E$30,24)</f>
+        <v/>
+      </c>
+      <c r="AD4" s="47">
+        <f>COUNTIF('평가'!$E$6:$E$30,25)</f>
         <v/>
       </c>
     </row>
@@ -16393,115 +17463,119 @@
         </is>
       </c>
       <c r="B5" s="46">
-        <f>COUNT('평가'!F6:F29)</f>
+        <f>COUNT('평가'!F6:F30)</f>
         <v/>
       </c>
       <c r="C5" s="46">
-        <f>COUNTIF(F5:AC5,"&gt;0")</f>
+        <f>COUNTIF(F5:AD5,"&gt;0")</f>
         <v/>
       </c>
       <c r="D5" s="46">
-        <f>MAX(F5:AC5)</f>
+        <f>MAX(F5:AD5)</f>
         <v/>
       </c>
       <c r="E5" s="46">
-        <f>IF(B5=0,"no response yet",IF(B5&lt;24,"missing depts",IF(C5=1,"all one group?",IF(C5&gt;18,"too many groups?","OK"))))</f>
+        <f>IF(B5=0,"no response yet",IF(B5&lt;25,"missing depts",IF(C5=1,"all one group?",IF(C5&gt;18,"too many groups?","OK"))))</f>
         <v/>
       </c>
       <c r="F5" s="47">
-        <f>COUNTIF('평가'!$F$6:$F$29,1)</f>
+        <f>COUNTIF('평가'!$F$6:$F$30,1)</f>
         <v/>
       </c>
       <c r="G5" s="47">
-        <f>COUNTIF('평가'!$F$6:$F$29,2)</f>
+        <f>COUNTIF('평가'!$F$6:$F$30,2)</f>
         <v/>
       </c>
       <c r="H5" s="47">
-        <f>COUNTIF('평가'!$F$6:$F$29,3)</f>
+        <f>COUNTIF('평가'!$F$6:$F$30,3)</f>
         <v/>
       </c>
       <c r="I5" s="47">
-        <f>COUNTIF('평가'!$F$6:$F$29,4)</f>
+        <f>COUNTIF('평가'!$F$6:$F$30,4)</f>
         <v/>
       </c>
       <c r="J5" s="47">
-        <f>COUNTIF('평가'!$F$6:$F$29,5)</f>
+        <f>COUNTIF('평가'!$F$6:$F$30,5)</f>
         <v/>
       </c>
       <c r="K5" s="47">
-        <f>COUNTIF('평가'!$F$6:$F$29,6)</f>
+        <f>COUNTIF('평가'!$F$6:$F$30,6)</f>
         <v/>
       </c>
       <c r="L5" s="47">
-        <f>COUNTIF('평가'!$F$6:$F$29,7)</f>
+        <f>COUNTIF('평가'!$F$6:$F$30,7)</f>
         <v/>
       </c>
       <c r="M5" s="47">
-        <f>COUNTIF('평가'!$F$6:$F$29,8)</f>
+        <f>COUNTIF('평가'!$F$6:$F$30,8)</f>
         <v/>
       </c>
       <c r="N5" s="47">
-        <f>COUNTIF('평가'!$F$6:$F$29,9)</f>
+        <f>COUNTIF('평가'!$F$6:$F$30,9)</f>
         <v/>
       </c>
       <c r="O5" s="47">
-        <f>COUNTIF('평가'!$F$6:$F$29,10)</f>
+        <f>COUNTIF('평가'!$F$6:$F$30,10)</f>
         <v/>
       </c>
       <c r="P5" s="47">
-        <f>COUNTIF('평가'!$F$6:$F$29,11)</f>
+        <f>COUNTIF('평가'!$F$6:$F$30,11)</f>
         <v/>
       </c>
       <c r="Q5" s="47">
-        <f>COUNTIF('평가'!$F$6:$F$29,12)</f>
+        <f>COUNTIF('평가'!$F$6:$F$30,12)</f>
         <v/>
       </c>
       <c r="R5" s="47">
-        <f>COUNTIF('평가'!$F$6:$F$29,13)</f>
+        <f>COUNTIF('평가'!$F$6:$F$30,13)</f>
         <v/>
       </c>
       <c r="S5" s="47">
-        <f>COUNTIF('평가'!$F$6:$F$29,14)</f>
+        <f>COUNTIF('평가'!$F$6:$F$30,14)</f>
         <v/>
       </c>
       <c r="T5" s="47">
-        <f>COUNTIF('평가'!$F$6:$F$29,15)</f>
+        <f>COUNTIF('평가'!$F$6:$F$30,15)</f>
         <v/>
       </c>
       <c r="U5" s="47">
-        <f>COUNTIF('평가'!$F$6:$F$29,16)</f>
+        <f>COUNTIF('평가'!$F$6:$F$30,16)</f>
         <v/>
       </c>
       <c r="V5" s="47">
-        <f>COUNTIF('평가'!$F$6:$F$29,17)</f>
+        <f>COUNTIF('평가'!$F$6:$F$30,17)</f>
         <v/>
       </c>
       <c r="W5" s="47">
-        <f>COUNTIF('평가'!$F$6:$F$29,18)</f>
+        <f>COUNTIF('평가'!$F$6:$F$30,18)</f>
         <v/>
       </c>
       <c r="X5" s="47">
-        <f>COUNTIF('평가'!$F$6:$F$29,19)</f>
+        <f>COUNTIF('평가'!$F$6:$F$30,19)</f>
         <v/>
       </c>
       <c r="Y5" s="47">
-        <f>COUNTIF('평가'!$F$6:$F$29,20)</f>
+        <f>COUNTIF('평가'!$F$6:$F$30,20)</f>
         <v/>
       </c>
       <c r="Z5" s="47">
-        <f>COUNTIF('평가'!$F$6:$F$29,21)</f>
+        <f>COUNTIF('평가'!$F$6:$F$30,21)</f>
         <v/>
       </c>
       <c r="AA5" s="47">
-        <f>COUNTIF('평가'!$F$6:$F$29,22)</f>
+        <f>COUNTIF('평가'!$F$6:$F$30,22)</f>
         <v/>
       </c>
       <c r="AB5" s="47">
-        <f>COUNTIF('평가'!$F$6:$F$29,23)</f>
+        <f>COUNTIF('평가'!$F$6:$F$30,23)</f>
         <v/>
       </c>
       <c r="AC5" s="47">
-        <f>COUNTIF('평가'!$F$6:$F$29,24)</f>
+        <f>COUNTIF('평가'!$F$6:$F$30,24)</f>
+        <v/>
+      </c>
+      <c r="AD5" s="47">
+        <f>COUNTIF('평가'!$F$6:$F$30,25)</f>
         <v/>
       </c>
     </row>
@@ -16512,115 +17586,119 @@
         </is>
       </c>
       <c r="B6" s="46">
-        <f>COUNT('평가'!G6:G29)</f>
+        <f>COUNT('평가'!G6:G30)</f>
         <v/>
       </c>
       <c r="C6" s="46">
-        <f>COUNTIF(F6:AC6,"&gt;0")</f>
+        <f>COUNTIF(F6:AD6,"&gt;0")</f>
         <v/>
       </c>
       <c r="D6" s="46">
-        <f>MAX(F6:AC6)</f>
+        <f>MAX(F6:AD6)</f>
         <v/>
       </c>
       <c r="E6" s="46">
-        <f>IF(B6=0,"no response yet",IF(B6&lt;24,"missing depts",IF(C6=1,"all one group?",IF(C6&gt;18,"too many groups?","OK"))))</f>
+        <f>IF(B6=0,"no response yet",IF(B6&lt;25,"missing depts",IF(C6=1,"all one group?",IF(C6&gt;18,"too many groups?","OK"))))</f>
         <v/>
       </c>
       <c r="F6" s="47">
-        <f>COUNTIF('평가'!$G$6:$G$29,1)</f>
+        <f>COUNTIF('평가'!$G$6:$G$30,1)</f>
         <v/>
       </c>
       <c r="G6" s="47">
-        <f>COUNTIF('평가'!$G$6:$G$29,2)</f>
+        <f>COUNTIF('평가'!$G$6:$G$30,2)</f>
         <v/>
       </c>
       <c r="H6" s="47">
-        <f>COUNTIF('평가'!$G$6:$G$29,3)</f>
+        <f>COUNTIF('평가'!$G$6:$G$30,3)</f>
         <v/>
       </c>
       <c r="I6" s="47">
-        <f>COUNTIF('평가'!$G$6:$G$29,4)</f>
+        <f>COUNTIF('평가'!$G$6:$G$30,4)</f>
         <v/>
       </c>
       <c r="J6" s="47">
-        <f>COUNTIF('평가'!$G$6:$G$29,5)</f>
+        <f>COUNTIF('평가'!$G$6:$G$30,5)</f>
         <v/>
       </c>
       <c r="K6" s="47">
-        <f>COUNTIF('평가'!$G$6:$G$29,6)</f>
+        <f>COUNTIF('평가'!$G$6:$G$30,6)</f>
         <v/>
       </c>
       <c r="L6" s="47">
-        <f>COUNTIF('평가'!$G$6:$G$29,7)</f>
+        <f>COUNTIF('평가'!$G$6:$G$30,7)</f>
         <v/>
       </c>
       <c r="M6" s="47">
-        <f>COUNTIF('평가'!$G$6:$G$29,8)</f>
+        <f>COUNTIF('평가'!$G$6:$G$30,8)</f>
         <v/>
       </c>
       <c r="N6" s="47">
-        <f>COUNTIF('평가'!$G$6:$G$29,9)</f>
+        <f>COUNTIF('평가'!$G$6:$G$30,9)</f>
         <v/>
       </c>
       <c r="O6" s="47">
-        <f>COUNTIF('평가'!$G$6:$G$29,10)</f>
+        <f>COUNTIF('평가'!$G$6:$G$30,10)</f>
         <v/>
       </c>
       <c r="P6" s="47">
-        <f>COUNTIF('평가'!$G$6:$G$29,11)</f>
+        <f>COUNTIF('평가'!$G$6:$G$30,11)</f>
         <v/>
       </c>
       <c r="Q6" s="47">
-        <f>COUNTIF('평가'!$G$6:$G$29,12)</f>
+        <f>COUNTIF('평가'!$G$6:$G$30,12)</f>
         <v/>
       </c>
       <c r="R6" s="47">
-        <f>COUNTIF('평가'!$G$6:$G$29,13)</f>
+        <f>COUNTIF('평가'!$G$6:$G$30,13)</f>
         <v/>
       </c>
       <c r="S6" s="47">
-        <f>COUNTIF('평가'!$G$6:$G$29,14)</f>
+        <f>COUNTIF('평가'!$G$6:$G$30,14)</f>
         <v/>
       </c>
       <c r="T6" s="47">
-        <f>COUNTIF('평가'!$G$6:$G$29,15)</f>
+        <f>COUNTIF('평가'!$G$6:$G$30,15)</f>
         <v/>
       </c>
       <c r="U6" s="47">
-        <f>COUNTIF('평가'!$G$6:$G$29,16)</f>
+        <f>COUNTIF('평가'!$G$6:$G$30,16)</f>
         <v/>
       </c>
       <c r="V6" s="47">
-        <f>COUNTIF('평가'!$G$6:$G$29,17)</f>
+        <f>COUNTIF('평가'!$G$6:$G$30,17)</f>
         <v/>
       </c>
       <c r="W6" s="47">
-        <f>COUNTIF('평가'!$G$6:$G$29,18)</f>
+        <f>COUNTIF('평가'!$G$6:$G$30,18)</f>
         <v/>
       </c>
       <c r="X6" s="47">
-        <f>COUNTIF('평가'!$G$6:$G$29,19)</f>
+        <f>COUNTIF('평가'!$G$6:$G$30,19)</f>
         <v/>
       </c>
       <c r="Y6" s="47">
-        <f>COUNTIF('평가'!$G$6:$G$29,20)</f>
+        <f>COUNTIF('평가'!$G$6:$G$30,20)</f>
         <v/>
       </c>
       <c r="Z6" s="47">
-        <f>COUNTIF('평가'!$G$6:$G$29,21)</f>
+        <f>COUNTIF('평가'!$G$6:$G$30,21)</f>
         <v/>
       </c>
       <c r="AA6" s="47">
-        <f>COUNTIF('평가'!$G$6:$G$29,22)</f>
+        <f>COUNTIF('평가'!$G$6:$G$30,22)</f>
         <v/>
       </c>
       <c r="AB6" s="47">
-        <f>COUNTIF('평가'!$G$6:$G$29,23)</f>
+        <f>COUNTIF('평가'!$G$6:$G$30,23)</f>
         <v/>
       </c>
       <c r="AC6" s="47">
-        <f>COUNTIF('평가'!$G$6:$G$29,24)</f>
+        <f>COUNTIF('평가'!$G$6:$G$30,24)</f>
+        <v/>
+      </c>
+      <c r="AD6" s="47">
+        <f>COUNTIF('평가'!$G$6:$G$30,25)</f>
         <v/>
       </c>
     </row>
@@ -16631,115 +17709,119 @@
         </is>
       </c>
       <c r="B7" s="46">
-        <f>COUNT('평가'!H6:H29)</f>
+        <f>COUNT('평가'!H6:H30)</f>
         <v/>
       </c>
       <c r="C7" s="46">
-        <f>COUNTIF(F7:AC7,"&gt;0")</f>
+        <f>COUNTIF(F7:AD7,"&gt;0")</f>
         <v/>
       </c>
       <c r="D7" s="46">
-        <f>MAX(F7:AC7)</f>
+        <f>MAX(F7:AD7)</f>
         <v/>
       </c>
       <c r="E7" s="46">
-        <f>IF(B7=0,"no response yet",IF(B7&lt;24,"missing depts",IF(C7=1,"all one group?",IF(C7&gt;18,"too many groups?","OK"))))</f>
+        <f>IF(B7=0,"no response yet",IF(B7&lt;25,"missing depts",IF(C7=1,"all one group?",IF(C7&gt;18,"too many groups?","OK"))))</f>
         <v/>
       </c>
       <c r="F7" s="47">
-        <f>COUNTIF('평가'!$H$6:$H$29,1)</f>
+        <f>COUNTIF('평가'!$H$6:$H$30,1)</f>
         <v/>
       </c>
       <c r="G7" s="47">
-        <f>COUNTIF('평가'!$H$6:$H$29,2)</f>
+        <f>COUNTIF('평가'!$H$6:$H$30,2)</f>
         <v/>
       </c>
       <c r="H7" s="47">
-        <f>COUNTIF('평가'!$H$6:$H$29,3)</f>
+        <f>COUNTIF('평가'!$H$6:$H$30,3)</f>
         <v/>
       </c>
       <c r="I7" s="47">
-        <f>COUNTIF('평가'!$H$6:$H$29,4)</f>
+        <f>COUNTIF('평가'!$H$6:$H$30,4)</f>
         <v/>
       </c>
       <c r="J7" s="47">
-        <f>COUNTIF('평가'!$H$6:$H$29,5)</f>
+        <f>COUNTIF('평가'!$H$6:$H$30,5)</f>
         <v/>
       </c>
       <c r="K7" s="47">
-        <f>COUNTIF('평가'!$H$6:$H$29,6)</f>
+        <f>COUNTIF('평가'!$H$6:$H$30,6)</f>
         <v/>
       </c>
       <c r="L7" s="47">
-        <f>COUNTIF('평가'!$H$6:$H$29,7)</f>
+        <f>COUNTIF('평가'!$H$6:$H$30,7)</f>
         <v/>
       </c>
       <c r="M7" s="47">
-        <f>COUNTIF('평가'!$H$6:$H$29,8)</f>
+        <f>COUNTIF('평가'!$H$6:$H$30,8)</f>
         <v/>
       </c>
       <c r="N7" s="47">
-        <f>COUNTIF('평가'!$H$6:$H$29,9)</f>
+        <f>COUNTIF('평가'!$H$6:$H$30,9)</f>
         <v/>
       </c>
       <c r="O7" s="47">
-        <f>COUNTIF('평가'!$H$6:$H$29,10)</f>
+        <f>COUNTIF('평가'!$H$6:$H$30,10)</f>
         <v/>
       </c>
       <c r="P7" s="47">
-        <f>COUNTIF('평가'!$H$6:$H$29,11)</f>
+        <f>COUNTIF('평가'!$H$6:$H$30,11)</f>
         <v/>
       </c>
       <c r="Q7" s="47">
-        <f>COUNTIF('평가'!$H$6:$H$29,12)</f>
+        <f>COUNTIF('평가'!$H$6:$H$30,12)</f>
         <v/>
       </c>
       <c r="R7" s="47">
-        <f>COUNTIF('평가'!$H$6:$H$29,13)</f>
+        <f>COUNTIF('평가'!$H$6:$H$30,13)</f>
         <v/>
       </c>
       <c r="S7" s="47">
-        <f>COUNTIF('평가'!$H$6:$H$29,14)</f>
+        <f>COUNTIF('평가'!$H$6:$H$30,14)</f>
         <v/>
       </c>
       <c r="T7" s="47">
-        <f>COUNTIF('평가'!$H$6:$H$29,15)</f>
+        <f>COUNTIF('평가'!$H$6:$H$30,15)</f>
         <v/>
       </c>
       <c r="U7" s="47">
-        <f>COUNTIF('평가'!$H$6:$H$29,16)</f>
+        <f>COUNTIF('평가'!$H$6:$H$30,16)</f>
         <v/>
       </c>
       <c r="V7" s="47">
-        <f>COUNTIF('평가'!$H$6:$H$29,17)</f>
+        <f>COUNTIF('평가'!$H$6:$H$30,17)</f>
         <v/>
       </c>
       <c r="W7" s="47">
-        <f>COUNTIF('평가'!$H$6:$H$29,18)</f>
+        <f>COUNTIF('평가'!$H$6:$H$30,18)</f>
         <v/>
       </c>
       <c r="X7" s="47">
-        <f>COUNTIF('평가'!$H$6:$H$29,19)</f>
+        <f>COUNTIF('평가'!$H$6:$H$30,19)</f>
         <v/>
       </c>
       <c r="Y7" s="47">
-        <f>COUNTIF('평가'!$H$6:$H$29,20)</f>
+        <f>COUNTIF('평가'!$H$6:$H$30,20)</f>
         <v/>
       </c>
       <c r="Z7" s="47">
-        <f>COUNTIF('평가'!$H$6:$H$29,21)</f>
+        <f>COUNTIF('평가'!$H$6:$H$30,21)</f>
         <v/>
       </c>
       <c r="AA7" s="47">
-        <f>COUNTIF('평가'!$H$6:$H$29,22)</f>
+        <f>COUNTIF('평가'!$H$6:$H$30,22)</f>
         <v/>
       </c>
       <c r="AB7" s="47">
-        <f>COUNTIF('평가'!$H$6:$H$29,23)</f>
+        <f>COUNTIF('평가'!$H$6:$H$30,23)</f>
         <v/>
       </c>
       <c r="AC7" s="47">
-        <f>COUNTIF('평가'!$H$6:$H$29,24)</f>
+        <f>COUNTIF('평가'!$H$6:$H$30,24)</f>
+        <v/>
+      </c>
+      <c r="AD7" s="47">
+        <f>COUNTIF('평가'!$H$6:$H$30,25)</f>
         <v/>
       </c>
     </row>
@@ -16750,115 +17832,119 @@
         </is>
       </c>
       <c r="B8" s="46">
-        <f>COUNT('평가'!I6:I29)</f>
+        <f>COUNT('평가'!I6:I30)</f>
         <v/>
       </c>
       <c r="C8" s="46">
-        <f>COUNTIF(F8:AC8,"&gt;0")</f>
+        <f>COUNTIF(F8:AD8,"&gt;0")</f>
         <v/>
       </c>
       <c r="D8" s="46">
-        <f>MAX(F8:AC8)</f>
+        <f>MAX(F8:AD8)</f>
         <v/>
       </c>
       <c r="E8" s="46">
-        <f>IF(B8=0,"no response yet",IF(B8&lt;24,"missing depts",IF(C8=1,"all one group?",IF(C8&gt;18,"too many groups?","OK"))))</f>
+        <f>IF(B8=0,"no response yet",IF(B8&lt;25,"missing depts",IF(C8=1,"all one group?",IF(C8&gt;18,"too many groups?","OK"))))</f>
         <v/>
       </c>
       <c r="F8" s="47">
-        <f>COUNTIF('평가'!$I$6:$I$29,1)</f>
+        <f>COUNTIF('평가'!$I$6:$I$30,1)</f>
         <v/>
       </c>
       <c r="G8" s="47">
-        <f>COUNTIF('평가'!$I$6:$I$29,2)</f>
+        <f>COUNTIF('평가'!$I$6:$I$30,2)</f>
         <v/>
       </c>
       <c r="H8" s="47">
-        <f>COUNTIF('평가'!$I$6:$I$29,3)</f>
+        <f>COUNTIF('평가'!$I$6:$I$30,3)</f>
         <v/>
       </c>
       <c r="I8" s="47">
-        <f>COUNTIF('평가'!$I$6:$I$29,4)</f>
+        <f>COUNTIF('평가'!$I$6:$I$30,4)</f>
         <v/>
       </c>
       <c r="J8" s="47">
-        <f>COUNTIF('평가'!$I$6:$I$29,5)</f>
+        <f>COUNTIF('평가'!$I$6:$I$30,5)</f>
         <v/>
       </c>
       <c r="K8" s="47">
-        <f>COUNTIF('평가'!$I$6:$I$29,6)</f>
+        <f>COUNTIF('평가'!$I$6:$I$30,6)</f>
         <v/>
       </c>
       <c r="L8" s="47">
-        <f>COUNTIF('평가'!$I$6:$I$29,7)</f>
+        <f>COUNTIF('평가'!$I$6:$I$30,7)</f>
         <v/>
       </c>
       <c r="M8" s="47">
-        <f>COUNTIF('평가'!$I$6:$I$29,8)</f>
+        <f>COUNTIF('평가'!$I$6:$I$30,8)</f>
         <v/>
       </c>
       <c r="N8" s="47">
-        <f>COUNTIF('평가'!$I$6:$I$29,9)</f>
+        <f>COUNTIF('평가'!$I$6:$I$30,9)</f>
         <v/>
       </c>
       <c r="O8" s="47">
-        <f>COUNTIF('평가'!$I$6:$I$29,10)</f>
+        <f>COUNTIF('평가'!$I$6:$I$30,10)</f>
         <v/>
       </c>
       <c r="P8" s="47">
-        <f>COUNTIF('평가'!$I$6:$I$29,11)</f>
+        <f>COUNTIF('평가'!$I$6:$I$30,11)</f>
         <v/>
       </c>
       <c r="Q8" s="47">
-        <f>COUNTIF('평가'!$I$6:$I$29,12)</f>
+        <f>COUNTIF('평가'!$I$6:$I$30,12)</f>
         <v/>
       </c>
       <c r="R8" s="47">
-        <f>COUNTIF('평가'!$I$6:$I$29,13)</f>
+        <f>COUNTIF('평가'!$I$6:$I$30,13)</f>
         <v/>
       </c>
       <c r="S8" s="47">
-        <f>COUNTIF('평가'!$I$6:$I$29,14)</f>
+        <f>COUNTIF('평가'!$I$6:$I$30,14)</f>
         <v/>
       </c>
       <c r="T8" s="47">
-        <f>COUNTIF('평가'!$I$6:$I$29,15)</f>
+        <f>COUNTIF('평가'!$I$6:$I$30,15)</f>
         <v/>
       </c>
       <c r="U8" s="47">
-        <f>COUNTIF('평가'!$I$6:$I$29,16)</f>
+        <f>COUNTIF('평가'!$I$6:$I$30,16)</f>
         <v/>
       </c>
       <c r="V8" s="47">
-        <f>COUNTIF('평가'!$I$6:$I$29,17)</f>
+        <f>COUNTIF('평가'!$I$6:$I$30,17)</f>
         <v/>
       </c>
       <c r="W8" s="47">
-        <f>COUNTIF('평가'!$I$6:$I$29,18)</f>
+        <f>COUNTIF('평가'!$I$6:$I$30,18)</f>
         <v/>
       </c>
       <c r="X8" s="47">
-        <f>COUNTIF('평가'!$I$6:$I$29,19)</f>
+        <f>COUNTIF('평가'!$I$6:$I$30,19)</f>
         <v/>
       </c>
       <c r="Y8" s="47">
-        <f>COUNTIF('평가'!$I$6:$I$29,20)</f>
+        <f>COUNTIF('평가'!$I$6:$I$30,20)</f>
         <v/>
       </c>
       <c r="Z8" s="47">
-        <f>COUNTIF('평가'!$I$6:$I$29,21)</f>
+        <f>COUNTIF('평가'!$I$6:$I$30,21)</f>
         <v/>
       </c>
       <c r="AA8" s="47">
-        <f>COUNTIF('평가'!$I$6:$I$29,22)</f>
+        <f>COUNTIF('평가'!$I$6:$I$30,22)</f>
         <v/>
       </c>
       <c r="AB8" s="47">
-        <f>COUNTIF('평가'!$I$6:$I$29,23)</f>
+        <f>COUNTIF('평가'!$I$6:$I$30,23)</f>
         <v/>
       </c>
       <c r="AC8" s="47">
-        <f>COUNTIF('평가'!$I$6:$I$29,24)</f>
+        <f>COUNTIF('평가'!$I$6:$I$30,24)</f>
+        <v/>
+      </c>
+      <c r="AD8" s="47">
+        <f>COUNTIF('평가'!$I$6:$I$30,25)</f>
         <v/>
       </c>
     </row>
@@ -16869,115 +17955,119 @@
         </is>
       </c>
       <c r="B9" s="46">
-        <f>COUNT('평가'!J6:J29)</f>
+        <f>COUNT('평가'!J6:J30)</f>
         <v/>
       </c>
       <c r="C9" s="46">
-        <f>COUNTIF(F9:AC9,"&gt;0")</f>
+        <f>COUNTIF(F9:AD9,"&gt;0")</f>
         <v/>
       </c>
       <c r="D9" s="46">
-        <f>MAX(F9:AC9)</f>
+        <f>MAX(F9:AD9)</f>
         <v/>
       </c>
       <c r="E9" s="46">
-        <f>IF(B9=0,"no response yet",IF(B9&lt;24,"missing depts",IF(C9=1,"all one group?",IF(C9&gt;18,"too many groups?","OK"))))</f>
+        <f>IF(B9=0,"no response yet",IF(B9&lt;25,"missing depts",IF(C9=1,"all one group?",IF(C9&gt;18,"too many groups?","OK"))))</f>
         <v/>
       </c>
       <c r="F9" s="47">
-        <f>COUNTIF('평가'!$J$6:$J$29,1)</f>
+        <f>COUNTIF('평가'!$J$6:$J$30,1)</f>
         <v/>
       </c>
       <c r="G9" s="47">
-        <f>COUNTIF('평가'!$J$6:$J$29,2)</f>
+        <f>COUNTIF('평가'!$J$6:$J$30,2)</f>
         <v/>
       </c>
       <c r="H9" s="47">
-        <f>COUNTIF('평가'!$J$6:$J$29,3)</f>
+        <f>COUNTIF('평가'!$J$6:$J$30,3)</f>
         <v/>
       </c>
       <c r="I9" s="47">
-        <f>COUNTIF('평가'!$J$6:$J$29,4)</f>
+        <f>COUNTIF('평가'!$J$6:$J$30,4)</f>
         <v/>
       </c>
       <c r="J9" s="47">
-        <f>COUNTIF('평가'!$J$6:$J$29,5)</f>
+        <f>COUNTIF('평가'!$J$6:$J$30,5)</f>
         <v/>
       </c>
       <c r="K9" s="47">
-        <f>COUNTIF('평가'!$J$6:$J$29,6)</f>
+        <f>COUNTIF('평가'!$J$6:$J$30,6)</f>
         <v/>
       </c>
       <c r="L9" s="47">
-        <f>COUNTIF('평가'!$J$6:$J$29,7)</f>
+        <f>COUNTIF('평가'!$J$6:$J$30,7)</f>
         <v/>
       </c>
       <c r="M9" s="47">
-        <f>COUNTIF('평가'!$J$6:$J$29,8)</f>
+        <f>COUNTIF('평가'!$J$6:$J$30,8)</f>
         <v/>
       </c>
       <c r="N9" s="47">
-        <f>COUNTIF('평가'!$J$6:$J$29,9)</f>
+        <f>COUNTIF('평가'!$J$6:$J$30,9)</f>
         <v/>
       </c>
       <c r="O9" s="47">
-        <f>COUNTIF('평가'!$J$6:$J$29,10)</f>
+        <f>COUNTIF('평가'!$J$6:$J$30,10)</f>
         <v/>
       </c>
       <c r="P9" s="47">
-        <f>COUNTIF('평가'!$J$6:$J$29,11)</f>
+        <f>COUNTIF('평가'!$J$6:$J$30,11)</f>
         <v/>
       </c>
       <c r="Q9" s="47">
-        <f>COUNTIF('평가'!$J$6:$J$29,12)</f>
+        <f>COUNTIF('평가'!$J$6:$J$30,12)</f>
         <v/>
       </c>
       <c r="R9" s="47">
-        <f>COUNTIF('평가'!$J$6:$J$29,13)</f>
+        <f>COUNTIF('평가'!$J$6:$J$30,13)</f>
         <v/>
       </c>
       <c r="S9" s="47">
-        <f>COUNTIF('평가'!$J$6:$J$29,14)</f>
+        <f>COUNTIF('평가'!$J$6:$J$30,14)</f>
         <v/>
       </c>
       <c r="T9" s="47">
-        <f>COUNTIF('평가'!$J$6:$J$29,15)</f>
+        <f>COUNTIF('평가'!$J$6:$J$30,15)</f>
         <v/>
       </c>
       <c r="U9" s="47">
-        <f>COUNTIF('평가'!$J$6:$J$29,16)</f>
+        <f>COUNTIF('평가'!$J$6:$J$30,16)</f>
         <v/>
       </c>
       <c r="V9" s="47">
-        <f>COUNTIF('평가'!$J$6:$J$29,17)</f>
+        <f>COUNTIF('평가'!$J$6:$J$30,17)</f>
         <v/>
       </c>
       <c r="W9" s="47">
-        <f>COUNTIF('평가'!$J$6:$J$29,18)</f>
+        <f>COUNTIF('평가'!$J$6:$J$30,18)</f>
         <v/>
       </c>
       <c r="X9" s="47">
-        <f>COUNTIF('평가'!$J$6:$J$29,19)</f>
+        <f>COUNTIF('평가'!$J$6:$J$30,19)</f>
         <v/>
       </c>
       <c r="Y9" s="47">
-        <f>COUNTIF('평가'!$J$6:$J$29,20)</f>
+        <f>COUNTIF('평가'!$J$6:$J$30,20)</f>
         <v/>
       </c>
       <c r="Z9" s="47">
-        <f>COUNTIF('평가'!$J$6:$J$29,21)</f>
+        <f>COUNTIF('평가'!$J$6:$J$30,21)</f>
         <v/>
       </c>
       <c r="AA9" s="47">
-        <f>COUNTIF('평가'!$J$6:$J$29,22)</f>
+        <f>COUNTIF('평가'!$J$6:$J$30,22)</f>
         <v/>
       </c>
       <c r="AB9" s="47">
-        <f>COUNTIF('평가'!$J$6:$J$29,23)</f>
+        <f>COUNTIF('평가'!$J$6:$J$30,23)</f>
         <v/>
       </c>
       <c r="AC9" s="47">
-        <f>COUNTIF('평가'!$J$6:$J$29,24)</f>
+        <f>COUNTIF('평가'!$J$6:$J$30,24)</f>
+        <v/>
+      </c>
+      <c r="AD9" s="47">
+        <f>COUNTIF('평가'!$J$6:$J$30,25)</f>
         <v/>
       </c>
     </row>
@@ -16988,115 +18078,119 @@
         </is>
       </c>
       <c r="B10" s="46">
-        <f>COUNT('평가'!K6:K29)</f>
+        <f>COUNT('평가'!K6:K30)</f>
         <v/>
       </c>
       <c r="C10" s="46">
-        <f>COUNTIF(F10:AC10,"&gt;0")</f>
+        <f>COUNTIF(F10:AD10,"&gt;0")</f>
         <v/>
       </c>
       <c r="D10" s="46">
-        <f>MAX(F10:AC10)</f>
+        <f>MAX(F10:AD10)</f>
         <v/>
       </c>
       <c r="E10" s="46">
-        <f>IF(B10=0,"no response yet",IF(B10&lt;24,"missing depts",IF(C10=1,"all one group?",IF(C10&gt;18,"too many groups?","OK"))))</f>
+        <f>IF(B10=0,"no response yet",IF(B10&lt;25,"missing depts",IF(C10=1,"all one group?",IF(C10&gt;18,"too many groups?","OK"))))</f>
         <v/>
       </c>
       <c r="F10" s="47">
-        <f>COUNTIF('평가'!$K$6:$K$29,1)</f>
+        <f>COUNTIF('평가'!$K$6:$K$30,1)</f>
         <v/>
       </c>
       <c r="G10" s="47">
-        <f>COUNTIF('평가'!$K$6:$K$29,2)</f>
+        <f>COUNTIF('평가'!$K$6:$K$30,2)</f>
         <v/>
       </c>
       <c r="H10" s="47">
-        <f>COUNTIF('평가'!$K$6:$K$29,3)</f>
+        <f>COUNTIF('평가'!$K$6:$K$30,3)</f>
         <v/>
       </c>
       <c r="I10" s="47">
-        <f>COUNTIF('평가'!$K$6:$K$29,4)</f>
+        <f>COUNTIF('평가'!$K$6:$K$30,4)</f>
         <v/>
       </c>
       <c r="J10" s="47">
-        <f>COUNTIF('평가'!$K$6:$K$29,5)</f>
+        <f>COUNTIF('평가'!$K$6:$K$30,5)</f>
         <v/>
       </c>
       <c r="K10" s="47">
-        <f>COUNTIF('평가'!$K$6:$K$29,6)</f>
+        <f>COUNTIF('평가'!$K$6:$K$30,6)</f>
         <v/>
       </c>
       <c r="L10" s="47">
-        <f>COUNTIF('평가'!$K$6:$K$29,7)</f>
+        <f>COUNTIF('평가'!$K$6:$K$30,7)</f>
         <v/>
       </c>
       <c r="M10" s="47">
-        <f>COUNTIF('평가'!$K$6:$K$29,8)</f>
+        <f>COUNTIF('평가'!$K$6:$K$30,8)</f>
         <v/>
       </c>
       <c r="N10" s="47">
-        <f>COUNTIF('평가'!$K$6:$K$29,9)</f>
+        <f>COUNTIF('평가'!$K$6:$K$30,9)</f>
         <v/>
       </c>
       <c r="O10" s="47">
-        <f>COUNTIF('평가'!$K$6:$K$29,10)</f>
+        <f>COUNTIF('평가'!$K$6:$K$30,10)</f>
         <v/>
       </c>
       <c r="P10" s="47">
-        <f>COUNTIF('평가'!$K$6:$K$29,11)</f>
+        <f>COUNTIF('평가'!$K$6:$K$30,11)</f>
         <v/>
       </c>
       <c r="Q10" s="47">
-        <f>COUNTIF('평가'!$K$6:$K$29,12)</f>
+        <f>COUNTIF('평가'!$K$6:$K$30,12)</f>
         <v/>
       </c>
       <c r="R10" s="47">
-        <f>COUNTIF('평가'!$K$6:$K$29,13)</f>
+        <f>COUNTIF('평가'!$K$6:$K$30,13)</f>
         <v/>
       </c>
       <c r="S10" s="47">
-        <f>COUNTIF('평가'!$K$6:$K$29,14)</f>
+        <f>COUNTIF('평가'!$K$6:$K$30,14)</f>
         <v/>
       </c>
       <c r="T10" s="47">
-        <f>COUNTIF('평가'!$K$6:$K$29,15)</f>
+        <f>COUNTIF('평가'!$K$6:$K$30,15)</f>
         <v/>
       </c>
       <c r="U10" s="47">
-        <f>COUNTIF('평가'!$K$6:$K$29,16)</f>
+        <f>COUNTIF('평가'!$K$6:$K$30,16)</f>
         <v/>
       </c>
       <c r="V10" s="47">
-        <f>COUNTIF('평가'!$K$6:$K$29,17)</f>
+        <f>COUNTIF('평가'!$K$6:$K$30,17)</f>
         <v/>
       </c>
       <c r="W10" s="47">
-        <f>COUNTIF('평가'!$K$6:$K$29,18)</f>
+        <f>COUNTIF('평가'!$K$6:$K$30,18)</f>
         <v/>
       </c>
       <c r="X10" s="47">
-        <f>COUNTIF('평가'!$K$6:$K$29,19)</f>
+        <f>COUNTIF('평가'!$K$6:$K$30,19)</f>
         <v/>
       </c>
       <c r="Y10" s="47">
-        <f>COUNTIF('평가'!$K$6:$K$29,20)</f>
+        <f>COUNTIF('평가'!$K$6:$K$30,20)</f>
         <v/>
       </c>
       <c r="Z10" s="47">
-        <f>COUNTIF('평가'!$K$6:$K$29,21)</f>
+        <f>COUNTIF('평가'!$K$6:$K$30,21)</f>
         <v/>
       </c>
       <c r="AA10" s="47">
-        <f>COUNTIF('평가'!$K$6:$K$29,22)</f>
+        <f>COUNTIF('평가'!$K$6:$K$30,22)</f>
         <v/>
       </c>
       <c r="AB10" s="47">
-        <f>COUNTIF('평가'!$K$6:$K$29,23)</f>
+        <f>COUNTIF('평가'!$K$6:$K$30,23)</f>
         <v/>
       </c>
       <c r="AC10" s="47">
-        <f>COUNTIF('평가'!$K$6:$K$29,24)</f>
+        <f>COUNTIF('평가'!$K$6:$K$30,24)</f>
+        <v/>
+      </c>
+      <c r="AD10" s="47">
+        <f>COUNTIF('평가'!$K$6:$K$30,25)</f>
         <v/>
       </c>
     </row>
@@ -17107,115 +18201,119 @@
         </is>
       </c>
       <c r="B11" s="46">
-        <f>COUNT('평가'!L6:L29)</f>
+        <f>COUNT('평가'!L6:L30)</f>
         <v/>
       </c>
       <c r="C11" s="46">
-        <f>COUNTIF(F11:AC11,"&gt;0")</f>
+        <f>COUNTIF(F11:AD11,"&gt;0")</f>
         <v/>
       </c>
       <c r="D11" s="46">
-        <f>MAX(F11:AC11)</f>
+        <f>MAX(F11:AD11)</f>
         <v/>
       </c>
       <c r="E11" s="46">
-        <f>IF(B11=0,"no response yet",IF(B11&lt;24,"missing depts",IF(C11=1,"all one group?",IF(C11&gt;18,"too many groups?","OK"))))</f>
+        <f>IF(B11=0,"no response yet",IF(B11&lt;25,"missing depts",IF(C11=1,"all one group?",IF(C11&gt;18,"too many groups?","OK"))))</f>
         <v/>
       </c>
       <c r="F11" s="47">
-        <f>COUNTIF('평가'!$L$6:$L$29,1)</f>
+        <f>COUNTIF('평가'!$L$6:$L$30,1)</f>
         <v/>
       </c>
       <c r="G11" s="47">
-        <f>COUNTIF('평가'!$L$6:$L$29,2)</f>
+        <f>COUNTIF('평가'!$L$6:$L$30,2)</f>
         <v/>
       </c>
       <c r="H11" s="47">
-        <f>COUNTIF('평가'!$L$6:$L$29,3)</f>
+        <f>COUNTIF('평가'!$L$6:$L$30,3)</f>
         <v/>
       </c>
       <c r="I11" s="47">
-        <f>COUNTIF('평가'!$L$6:$L$29,4)</f>
+        <f>COUNTIF('평가'!$L$6:$L$30,4)</f>
         <v/>
       </c>
       <c r="J11" s="47">
-        <f>COUNTIF('평가'!$L$6:$L$29,5)</f>
+        <f>COUNTIF('평가'!$L$6:$L$30,5)</f>
         <v/>
       </c>
       <c r="K11" s="47">
-        <f>COUNTIF('평가'!$L$6:$L$29,6)</f>
+        <f>COUNTIF('평가'!$L$6:$L$30,6)</f>
         <v/>
       </c>
       <c r="L11" s="47">
-        <f>COUNTIF('평가'!$L$6:$L$29,7)</f>
+        <f>COUNTIF('평가'!$L$6:$L$30,7)</f>
         <v/>
       </c>
       <c r="M11" s="47">
-        <f>COUNTIF('평가'!$L$6:$L$29,8)</f>
+        <f>COUNTIF('평가'!$L$6:$L$30,8)</f>
         <v/>
       </c>
       <c r="N11" s="47">
-        <f>COUNTIF('평가'!$L$6:$L$29,9)</f>
+        <f>COUNTIF('평가'!$L$6:$L$30,9)</f>
         <v/>
       </c>
       <c r="O11" s="47">
-        <f>COUNTIF('평가'!$L$6:$L$29,10)</f>
+        <f>COUNTIF('평가'!$L$6:$L$30,10)</f>
         <v/>
       </c>
       <c r="P11" s="47">
-        <f>COUNTIF('평가'!$L$6:$L$29,11)</f>
+        <f>COUNTIF('평가'!$L$6:$L$30,11)</f>
         <v/>
       </c>
       <c r="Q11" s="47">
-        <f>COUNTIF('평가'!$L$6:$L$29,12)</f>
+        <f>COUNTIF('평가'!$L$6:$L$30,12)</f>
         <v/>
       </c>
       <c r="R11" s="47">
-        <f>COUNTIF('평가'!$L$6:$L$29,13)</f>
+        <f>COUNTIF('평가'!$L$6:$L$30,13)</f>
         <v/>
       </c>
       <c r="S11" s="47">
-        <f>COUNTIF('평가'!$L$6:$L$29,14)</f>
+        <f>COUNTIF('평가'!$L$6:$L$30,14)</f>
         <v/>
       </c>
       <c r="T11" s="47">
-        <f>COUNTIF('평가'!$L$6:$L$29,15)</f>
+        <f>COUNTIF('평가'!$L$6:$L$30,15)</f>
         <v/>
       </c>
       <c r="U11" s="47">
-        <f>COUNTIF('평가'!$L$6:$L$29,16)</f>
+        <f>COUNTIF('평가'!$L$6:$L$30,16)</f>
         <v/>
       </c>
       <c r="V11" s="47">
-        <f>COUNTIF('평가'!$L$6:$L$29,17)</f>
+        <f>COUNTIF('평가'!$L$6:$L$30,17)</f>
         <v/>
       </c>
       <c r="W11" s="47">
-        <f>COUNTIF('평가'!$L$6:$L$29,18)</f>
+        <f>COUNTIF('평가'!$L$6:$L$30,18)</f>
         <v/>
       </c>
       <c r="X11" s="47">
-        <f>COUNTIF('평가'!$L$6:$L$29,19)</f>
+        <f>COUNTIF('평가'!$L$6:$L$30,19)</f>
         <v/>
       </c>
       <c r="Y11" s="47">
-        <f>COUNTIF('평가'!$L$6:$L$29,20)</f>
+        <f>COUNTIF('평가'!$L$6:$L$30,20)</f>
         <v/>
       </c>
       <c r="Z11" s="47">
-        <f>COUNTIF('평가'!$L$6:$L$29,21)</f>
+        <f>COUNTIF('평가'!$L$6:$L$30,21)</f>
         <v/>
       </c>
       <c r="AA11" s="47">
-        <f>COUNTIF('평가'!$L$6:$L$29,22)</f>
+        <f>COUNTIF('평가'!$L$6:$L$30,22)</f>
         <v/>
       </c>
       <c r="AB11" s="47">
-        <f>COUNTIF('평가'!$L$6:$L$29,23)</f>
+        <f>COUNTIF('평가'!$L$6:$L$30,23)</f>
         <v/>
       </c>
       <c r="AC11" s="47">
-        <f>COUNTIF('평가'!$L$6:$L$29,24)</f>
+        <f>COUNTIF('평가'!$L$6:$L$30,24)</f>
+        <v/>
+      </c>
+      <c r="AD11" s="47">
+        <f>COUNTIF('평가'!$L$6:$L$30,25)</f>
         <v/>
       </c>
     </row>
@@ -17226,115 +18324,119 @@
         </is>
       </c>
       <c r="B12" s="46">
-        <f>COUNT('평가'!M6:M29)</f>
+        <f>COUNT('평가'!M6:M30)</f>
         <v/>
       </c>
       <c r="C12" s="46">
-        <f>COUNTIF(F12:AC12,"&gt;0")</f>
+        <f>COUNTIF(F12:AD12,"&gt;0")</f>
         <v/>
       </c>
       <c r="D12" s="46">
-        <f>MAX(F12:AC12)</f>
+        <f>MAX(F12:AD12)</f>
         <v/>
       </c>
       <c r="E12" s="46">
-        <f>IF(B12=0,"no response yet",IF(B12&lt;24,"missing depts",IF(C12=1,"all one group?",IF(C12&gt;18,"too many groups?","OK"))))</f>
+        <f>IF(B12=0,"no response yet",IF(B12&lt;25,"missing depts",IF(C12=1,"all one group?",IF(C12&gt;18,"too many groups?","OK"))))</f>
         <v/>
       </c>
       <c r="F12" s="47">
-        <f>COUNTIF('평가'!$M$6:$M$29,1)</f>
+        <f>COUNTIF('평가'!$M$6:$M$30,1)</f>
         <v/>
       </c>
       <c r="G12" s="47">
-        <f>COUNTIF('평가'!$M$6:$M$29,2)</f>
+        <f>COUNTIF('평가'!$M$6:$M$30,2)</f>
         <v/>
       </c>
       <c r="H12" s="47">
-        <f>COUNTIF('평가'!$M$6:$M$29,3)</f>
+        <f>COUNTIF('평가'!$M$6:$M$30,3)</f>
         <v/>
       </c>
       <c r="I12" s="47">
-        <f>COUNTIF('평가'!$M$6:$M$29,4)</f>
+        <f>COUNTIF('평가'!$M$6:$M$30,4)</f>
         <v/>
       </c>
       <c r="J12" s="47">
-        <f>COUNTIF('평가'!$M$6:$M$29,5)</f>
+        <f>COUNTIF('평가'!$M$6:$M$30,5)</f>
         <v/>
       </c>
       <c r="K12" s="47">
-        <f>COUNTIF('평가'!$M$6:$M$29,6)</f>
+        <f>COUNTIF('평가'!$M$6:$M$30,6)</f>
         <v/>
       </c>
       <c r="L12" s="47">
-        <f>COUNTIF('평가'!$M$6:$M$29,7)</f>
+        <f>COUNTIF('평가'!$M$6:$M$30,7)</f>
         <v/>
       </c>
       <c r="M12" s="47">
-        <f>COUNTIF('평가'!$M$6:$M$29,8)</f>
+        <f>COUNTIF('평가'!$M$6:$M$30,8)</f>
         <v/>
       </c>
       <c r="N12" s="47">
-        <f>COUNTIF('평가'!$M$6:$M$29,9)</f>
+        <f>COUNTIF('평가'!$M$6:$M$30,9)</f>
         <v/>
       </c>
       <c r="O12" s="47">
-        <f>COUNTIF('평가'!$M$6:$M$29,10)</f>
+        <f>COUNTIF('평가'!$M$6:$M$30,10)</f>
         <v/>
       </c>
       <c r="P12" s="47">
-        <f>COUNTIF('평가'!$M$6:$M$29,11)</f>
+        <f>COUNTIF('평가'!$M$6:$M$30,11)</f>
         <v/>
       </c>
       <c r="Q12" s="47">
-        <f>COUNTIF('평가'!$M$6:$M$29,12)</f>
+        <f>COUNTIF('평가'!$M$6:$M$30,12)</f>
         <v/>
       </c>
       <c r="R12" s="47">
-        <f>COUNTIF('평가'!$M$6:$M$29,13)</f>
+        <f>COUNTIF('평가'!$M$6:$M$30,13)</f>
         <v/>
       </c>
       <c r="S12" s="47">
-        <f>COUNTIF('평가'!$M$6:$M$29,14)</f>
+        <f>COUNTIF('평가'!$M$6:$M$30,14)</f>
         <v/>
       </c>
       <c r="T12" s="47">
-        <f>COUNTIF('평가'!$M$6:$M$29,15)</f>
+        <f>COUNTIF('평가'!$M$6:$M$30,15)</f>
         <v/>
       </c>
       <c r="U12" s="47">
-        <f>COUNTIF('평가'!$M$6:$M$29,16)</f>
+        <f>COUNTIF('평가'!$M$6:$M$30,16)</f>
         <v/>
       </c>
       <c r="V12" s="47">
-        <f>COUNTIF('평가'!$M$6:$M$29,17)</f>
+        <f>COUNTIF('평가'!$M$6:$M$30,17)</f>
         <v/>
       </c>
       <c r="W12" s="47">
-        <f>COUNTIF('평가'!$M$6:$M$29,18)</f>
+        <f>COUNTIF('평가'!$M$6:$M$30,18)</f>
         <v/>
       </c>
       <c r="X12" s="47">
-        <f>COUNTIF('평가'!$M$6:$M$29,19)</f>
+        <f>COUNTIF('평가'!$M$6:$M$30,19)</f>
         <v/>
       </c>
       <c r="Y12" s="47">
-        <f>COUNTIF('평가'!$M$6:$M$29,20)</f>
+        <f>COUNTIF('평가'!$M$6:$M$30,20)</f>
         <v/>
       </c>
       <c r="Z12" s="47">
-        <f>COUNTIF('평가'!$M$6:$M$29,21)</f>
+        <f>COUNTIF('평가'!$M$6:$M$30,21)</f>
         <v/>
       </c>
       <c r="AA12" s="47">
-        <f>COUNTIF('평가'!$M$6:$M$29,22)</f>
+        <f>COUNTIF('평가'!$M$6:$M$30,22)</f>
         <v/>
       </c>
       <c r="AB12" s="47">
-        <f>COUNTIF('평가'!$M$6:$M$29,23)</f>
+        <f>COUNTIF('평가'!$M$6:$M$30,23)</f>
         <v/>
       </c>
       <c r="AC12" s="47">
-        <f>COUNTIF('평가'!$M$6:$M$29,24)</f>
+        <f>COUNTIF('평가'!$M$6:$M$30,24)</f>
+        <v/>
+      </c>
+      <c r="AD12" s="47">
+        <f>COUNTIF('평가'!$M$6:$M$30,25)</f>
         <v/>
       </c>
     </row>
@@ -17345,115 +18447,119 @@
         </is>
       </c>
       <c r="B13" s="46">
-        <f>COUNT('평가'!N6:N29)</f>
+        <f>COUNT('평가'!N6:N30)</f>
         <v/>
       </c>
       <c r="C13" s="46">
-        <f>COUNTIF(F13:AC13,"&gt;0")</f>
+        <f>COUNTIF(F13:AD13,"&gt;0")</f>
         <v/>
       </c>
       <c r="D13" s="46">
-        <f>MAX(F13:AC13)</f>
+        <f>MAX(F13:AD13)</f>
         <v/>
       </c>
       <c r="E13" s="46">
-        <f>IF(B13=0,"no response yet",IF(B13&lt;24,"missing depts",IF(C13=1,"all one group?",IF(C13&gt;18,"too many groups?","OK"))))</f>
+        <f>IF(B13=0,"no response yet",IF(B13&lt;25,"missing depts",IF(C13=1,"all one group?",IF(C13&gt;18,"too many groups?","OK"))))</f>
         <v/>
       </c>
       <c r="F13" s="47">
-        <f>COUNTIF('평가'!$N$6:$N$29,1)</f>
+        <f>COUNTIF('평가'!$N$6:$N$30,1)</f>
         <v/>
       </c>
       <c r="G13" s="47">
-        <f>COUNTIF('평가'!$N$6:$N$29,2)</f>
+        <f>COUNTIF('평가'!$N$6:$N$30,2)</f>
         <v/>
       </c>
       <c r="H13" s="47">
-        <f>COUNTIF('평가'!$N$6:$N$29,3)</f>
+        <f>COUNTIF('평가'!$N$6:$N$30,3)</f>
         <v/>
       </c>
       <c r="I13" s="47">
-        <f>COUNTIF('평가'!$N$6:$N$29,4)</f>
+        <f>COUNTIF('평가'!$N$6:$N$30,4)</f>
         <v/>
       </c>
       <c r="J13" s="47">
-        <f>COUNTIF('평가'!$N$6:$N$29,5)</f>
+        <f>COUNTIF('평가'!$N$6:$N$30,5)</f>
         <v/>
       </c>
       <c r="K13" s="47">
-        <f>COUNTIF('평가'!$N$6:$N$29,6)</f>
+        <f>COUNTIF('평가'!$N$6:$N$30,6)</f>
         <v/>
       </c>
       <c r="L13" s="47">
-        <f>COUNTIF('평가'!$N$6:$N$29,7)</f>
+        <f>COUNTIF('평가'!$N$6:$N$30,7)</f>
         <v/>
       </c>
       <c r="M13" s="47">
-        <f>COUNTIF('평가'!$N$6:$N$29,8)</f>
+        <f>COUNTIF('평가'!$N$6:$N$30,8)</f>
         <v/>
       </c>
       <c r="N13" s="47">
-        <f>COUNTIF('평가'!$N$6:$N$29,9)</f>
+        <f>COUNTIF('평가'!$N$6:$N$30,9)</f>
         <v/>
       </c>
       <c r="O13" s="47">
-        <f>COUNTIF('평가'!$N$6:$N$29,10)</f>
+        <f>COUNTIF('평가'!$N$6:$N$30,10)</f>
         <v/>
       </c>
       <c r="P13" s="47">
-        <f>COUNTIF('평가'!$N$6:$N$29,11)</f>
+        <f>COUNTIF('평가'!$N$6:$N$30,11)</f>
         <v/>
       </c>
       <c r="Q13" s="47">
-        <f>COUNTIF('평가'!$N$6:$N$29,12)</f>
+        <f>COUNTIF('평가'!$N$6:$N$30,12)</f>
         <v/>
       </c>
       <c r="R13" s="47">
-        <f>COUNTIF('평가'!$N$6:$N$29,13)</f>
+        <f>COUNTIF('평가'!$N$6:$N$30,13)</f>
         <v/>
       </c>
       <c r="S13" s="47">
-        <f>COUNTIF('평가'!$N$6:$N$29,14)</f>
+        <f>COUNTIF('평가'!$N$6:$N$30,14)</f>
         <v/>
       </c>
       <c r="T13" s="47">
-        <f>COUNTIF('평가'!$N$6:$N$29,15)</f>
+        <f>COUNTIF('평가'!$N$6:$N$30,15)</f>
         <v/>
       </c>
       <c r="U13" s="47">
-        <f>COUNTIF('평가'!$N$6:$N$29,16)</f>
+        <f>COUNTIF('평가'!$N$6:$N$30,16)</f>
         <v/>
       </c>
       <c r="V13" s="47">
-        <f>COUNTIF('평가'!$N$6:$N$29,17)</f>
+        <f>COUNTIF('평가'!$N$6:$N$30,17)</f>
         <v/>
       </c>
       <c r="W13" s="47">
-        <f>COUNTIF('평가'!$N$6:$N$29,18)</f>
+        <f>COUNTIF('평가'!$N$6:$N$30,18)</f>
         <v/>
       </c>
       <c r="X13" s="47">
-        <f>COUNTIF('평가'!$N$6:$N$29,19)</f>
+        <f>COUNTIF('평가'!$N$6:$N$30,19)</f>
         <v/>
       </c>
       <c r="Y13" s="47">
-        <f>COUNTIF('평가'!$N$6:$N$29,20)</f>
+        <f>COUNTIF('평가'!$N$6:$N$30,20)</f>
         <v/>
       </c>
       <c r="Z13" s="47">
-        <f>COUNTIF('평가'!$N$6:$N$29,21)</f>
+        <f>COUNTIF('평가'!$N$6:$N$30,21)</f>
         <v/>
       </c>
       <c r="AA13" s="47">
-        <f>COUNTIF('평가'!$N$6:$N$29,22)</f>
+        <f>COUNTIF('평가'!$N$6:$N$30,22)</f>
         <v/>
       </c>
       <c r="AB13" s="47">
-        <f>COUNTIF('평가'!$N$6:$N$29,23)</f>
+        <f>COUNTIF('평가'!$N$6:$N$30,23)</f>
         <v/>
       </c>
       <c r="AC13" s="47">
-        <f>COUNTIF('평가'!$N$6:$N$29,24)</f>
+        <f>COUNTIF('평가'!$N$6:$N$30,24)</f>
+        <v/>
+      </c>
+      <c r="AD13" s="47">
+        <f>COUNTIF('평가'!$N$6:$N$30,25)</f>
         <v/>
       </c>
     </row>
@@ -17464,115 +18570,119 @@
         </is>
       </c>
       <c r="B14" s="46">
-        <f>COUNT('평가'!O6:O29)</f>
+        <f>COUNT('평가'!O6:O30)</f>
         <v/>
       </c>
       <c r="C14" s="46">
-        <f>COUNTIF(F14:AC14,"&gt;0")</f>
+        <f>COUNTIF(F14:AD14,"&gt;0")</f>
         <v/>
       </c>
       <c r="D14" s="46">
-        <f>MAX(F14:AC14)</f>
+        <f>MAX(F14:AD14)</f>
         <v/>
       </c>
       <c r="E14" s="46">
-        <f>IF(B14=0,"no response yet",IF(B14&lt;24,"missing depts",IF(C14=1,"all one group?",IF(C14&gt;18,"too many groups?","OK"))))</f>
+        <f>IF(B14=0,"no response yet",IF(B14&lt;25,"missing depts",IF(C14=1,"all one group?",IF(C14&gt;18,"too many groups?","OK"))))</f>
         <v/>
       </c>
       <c r="F14" s="47">
-        <f>COUNTIF('평가'!$O$6:$O$29,1)</f>
+        <f>COUNTIF('평가'!$O$6:$O$30,1)</f>
         <v/>
       </c>
       <c r="G14" s="47">
-        <f>COUNTIF('평가'!$O$6:$O$29,2)</f>
+        <f>COUNTIF('평가'!$O$6:$O$30,2)</f>
         <v/>
       </c>
       <c r="H14" s="47">
-        <f>COUNTIF('평가'!$O$6:$O$29,3)</f>
+        <f>COUNTIF('평가'!$O$6:$O$30,3)</f>
         <v/>
       </c>
       <c r="I14" s="47">
-        <f>COUNTIF('평가'!$O$6:$O$29,4)</f>
+        <f>COUNTIF('평가'!$O$6:$O$30,4)</f>
         <v/>
       </c>
       <c r="J14" s="47">
-        <f>COUNTIF('평가'!$O$6:$O$29,5)</f>
+        <f>COUNTIF('평가'!$O$6:$O$30,5)</f>
         <v/>
       </c>
       <c r="K14" s="47">
-        <f>COUNTIF('평가'!$O$6:$O$29,6)</f>
+        <f>COUNTIF('평가'!$O$6:$O$30,6)</f>
         <v/>
       </c>
       <c r="L14" s="47">
-        <f>COUNTIF('평가'!$O$6:$O$29,7)</f>
+        <f>COUNTIF('평가'!$O$6:$O$30,7)</f>
         <v/>
       </c>
       <c r="M14" s="47">
-        <f>COUNTIF('평가'!$O$6:$O$29,8)</f>
+        <f>COUNTIF('평가'!$O$6:$O$30,8)</f>
         <v/>
       </c>
       <c r="N14" s="47">
-        <f>COUNTIF('평가'!$O$6:$O$29,9)</f>
+        <f>COUNTIF('평가'!$O$6:$O$30,9)</f>
         <v/>
       </c>
       <c r="O14" s="47">
-        <f>COUNTIF('평가'!$O$6:$O$29,10)</f>
+        <f>COUNTIF('평가'!$O$6:$O$30,10)</f>
         <v/>
       </c>
       <c r="P14" s="47">
-        <f>COUNTIF('평가'!$O$6:$O$29,11)</f>
+        <f>COUNTIF('평가'!$O$6:$O$30,11)</f>
         <v/>
       </c>
       <c r="Q14" s="47">
-        <f>COUNTIF('평가'!$O$6:$O$29,12)</f>
+        <f>COUNTIF('평가'!$O$6:$O$30,12)</f>
         <v/>
       </c>
       <c r="R14" s="47">
-        <f>COUNTIF('평가'!$O$6:$O$29,13)</f>
+        <f>COUNTIF('평가'!$O$6:$O$30,13)</f>
         <v/>
       </c>
       <c r="S14" s="47">
-        <f>COUNTIF('평가'!$O$6:$O$29,14)</f>
+        <f>COUNTIF('평가'!$O$6:$O$30,14)</f>
         <v/>
       </c>
       <c r="T14" s="47">
-        <f>COUNTIF('평가'!$O$6:$O$29,15)</f>
+        <f>COUNTIF('평가'!$O$6:$O$30,15)</f>
         <v/>
       </c>
       <c r="U14" s="47">
-        <f>COUNTIF('평가'!$O$6:$O$29,16)</f>
+        <f>COUNTIF('평가'!$O$6:$O$30,16)</f>
         <v/>
       </c>
       <c r="V14" s="47">
-        <f>COUNTIF('평가'!$O$6:$O$29,17)</f>
+        <f>COUNTIF('평가'!$O$6:$O$30,17)</f>
         <v/>
       </c>
       <c r="W14" s="47">
-        <f>COUNTIF('평가'!$O$6:$O$29,18)</f>
+        <f>COUNTIF('평가'!$O$6:$O$30,18)</f>
         <v/>
       </c>
       <c r="X14" s="47">
-        <f>COUNTIF('평가'!$O$6:$O$29,19)</f>
+        <f>COUNTIF('평가'!$O$6:$O$30,19)</f>
         <v/>
       </c>
       <c r="Y14" s="47">
-        <f>COUNTIF('평가'!$O$6:$O$29,20)</f>
+        <f>COUNTIF('평가'!$O$6:$O$30,20)</f>
         <v/>
       </c>
       <c r="Z14" s="47">
-        <f>COUNTIF('평가'!$O$6:$O$29,21)</f>
+        <f>COUNTIF('평가'!$O$6:$O$30,21)</f>
         <v/>
       </c>
       <c r="AA14" s="47">
-        <f>COUNTIF('평가'!$O$6:$O$29,22)</f>
+        <f>COUNTIF('평가'!$O$6:$O$30,22)</f>
         <v/>
       </c>
       <c r="AB14" s="47">
-        <f>COUNTIF('평가'!$O$6:$O$29,23)</f>
+        <f>COUNTIF('평가'!$O$6:$O$30,23)</f>
         <v/>
       </c>
       <c r="AC14" s="47">
-        <f>COUNTIF('평가'!$O$6:$O$29,24)</f>
+        <f>COUNTIF('평가'!$O$6:$O$30,24)</f>
+        <v/>
+      </c>
+      <c r="AD14" s="47">
+        <f>COUNTIF('평가'!$O$6:$O$30,25)</f>
         <v/>
       </c>
     </row>
@@ -17583,115 +18693,119 @@
         </is>
       </c>
       <c r="B15" s="46">
-        <f>COUNT('평가'!P6:P29)</f>
+        <f>COUNT('평가'!P6:P30)</f>
         <v/>
       </c>
       <c r="C15" s="46">
-        <f>COUNTIF(F15:AC15,"&gt;0")</f>
+        <f>COUNTIF(F15:AD15,"&gt;0")</f>
         <v/>
       </c>
       <c r="D15" s="46">
-        <f>MAX(F15:AC15)</f>
+        <f>MAX(F15:AD15)</f>
         <v/>
       </c>
       <c r="E15" s="46">
-        <f>IF(B15=0,"no response yet",IF(B15&lt;24,"missing depts",IF(C15=1,"all one group?",IF(C15&gt;18,"too many groups?","OK"))))</f>
+        <f>IF(B15=0,"no response yet",IF(B15&lt;25,"missing depts",IF(C15=1,"all one group?",IF(C15&gt;18,"too many groups?","OK"))))</f>
         <v/>
       </c>
       <c r="F15" s="47">
-        <f>COUNTIF('평가'!$P$6:$P$29,1)</f>
+        <f>COUNTIF('평가'!$P$6:$P$30,1)</f>
         <v/>
       </c>
       <c r="G15" s="47">
-        <f>COUNTIF('평가'!$P$6:$P$29,2)</f>
+        <f>COUNTIF('평가'!$P$6:$P$30,2)</f>
         <v/>
       </c>
       <c r="H15" s="47">
-        <f>COUNTIF('평가'!$P$6:$P$29,3)</f>
+        <f>COUNTIF('평가'!$P$6:$P$30,3)</f>
         <v/>
       </c>
       <c r="I15" s="47">
-        <f>COUNTIF('평가'!$P$6:$P$29,4)</f>
+        <f>COUNTIF('평가'!$P$6:$P$30,4)</f>
         <v/>
       </c>
       <c r="J15" s="47">
-        <f>COUNTIF('평가'!$P$6:$P$29,5)</f>
+        <f>COUNTIF('평가'!$P$6:$P$30,5)</f>
         <v/>
       </c>
       <c r="K15" s="47">
-        <f>COUNTIF('평가'!$P$6:$P$29,6)</f>
+        <f>COUNTIF('평가'!$P$6:$P$30,6)</f>
         <v/>
       </c>
       <c r="L15" s="47">
-        <f>COUNTIF('평가'!$P$6:$P$29,7)</f>
+        <f>COUNTIF('평가'!$P$6:$P$30,7)</f>
         <v/>
       </c>
       <c r="M15" s="47">
-        <f>COUNTIF('평가'!$P$6:$P$29,8)</f>
+        <f>COUNTIF('평가'!$P$6:$P$30,8)</f>
         <v/>
       </c>
       <c r="N15" s="47">
-        <f>COUNTIF('평가'!$P$6:$P$29,9)</f>
+        <f>COUNTIF('평가'!$P$6:$P$30,9)</f>
         <v/>
       </c>
       <c r="O15" s="47">
-        <f>COUNTIF('평가'!$P$6:$P$29,10)</f>
+        <f>COUNTIF('평가'!$P$6:$P$30,10)</f>
         <v/>
       </c>
       <c r="P15" s="47">
-        <f>COUNTIF('평가'!$P$6:$P$29,11)</f>
+        <f>COUNTIF('평가'!$P$6:$P$30,11)</f>
         <v/>
       </c>
       <c r="Q15" s="47">
-        <f>COUNTIF('평가'!$P$6:$P$29,12)</f>
+        <f>COUNTIF('평가'!$P$6:$P$30,12)</f>
         <v/>
       </c>
       <c r="R15" s="47">
-        <f>COUNTIF('평가'!$P$6:$P$29,13)</f>
+        <f>COUNTIF('평가'!$P$6:$P$30,13)</f>
         <v/>
       </c>
       <c r="S15" s="47">
-        <f>COUNTIF('평가'!$P$6:$P$29,14)</f>
+        <f>COUNTIF('평가'!$P$6:$P$30,14)</f>
         <v/>
       </c>
       <c r="T15" s="47">
-        <f>COUNTIF('평가'!$P$6:$P$29,15)</f>
+        <f>COUNTIF('평가'!$P$6:$P$30,15)</f>
         <v/>
       </c>
       <c r="U15" s="47">
-        <f>COUNTIF('평가'!$P$6:$P$29,16)</f>
+        <f>COUNTIF('평가'!$P$6:$P$30,16)</f>
         <v/>
       </c>
       <c r="V15" s="47">
-        <f>COUNTIF('평가'!$P$6:$P$29,17)</f>
+        <f>COUNTIF('평가'!$P$6:$P$30,17)</f>
         <v/>
       </c>
       <c r="W15" s="47">
-        <f>COUNTIF('평가'!$P$6:$P$29,18)</f>
+        <f>COUNTIF('평가'!$P$6:$P$30,18)</f>
         <v/>
       </c>
       <c r="X15" s="47">
-        <f>COUNTIF('평가'!$P$6:$P$29,19)</f>
+        <f>COUNTIF('평가'!$P$6:$P$30,19)</f>
         <v/>
       </c>
       <c r="Y15" s="47">
-        <f>COUNTIF('평가'!$P$6:$P$29,20)</f>
+        <f>COUNTIF('평가'!$P$6:$P$30,20)</f>
         <v/>
       </c>
       <c r="Z15" s="47">
-        <f>COUNTIF('평가'!$P$6:$P$29,21)</f>
+        <f>COUNTIF('평가'!$P$6:$P$30,21)</f>
         <v/>
       </c>
       <c r="AA15" s="47">
-        <f>COUNTIF('평가'!$P$6:$P$29,22)</f>
+        <f>COUNTIF('평가'!$P$6:$P$30,22)</f>
         <v/>
       </c>
       <c r="AB15" s="47">
-        <f>COUNTIF('평가'!$P$6:$P$29,23)</f>
+        <f>COUNTIF('평가'!$P$6:$P$30,23)</f>
         <v/>
       </c>
       <c r="AC15" s="47">
-        <f>COUNTIF('평가'!$P$6:$P$29,24)</f>
+        <f>COUNTIF('평가'!$P$6:$P$30,24)</f>
+        <v/>
+      </c>
+      <c r="AD15" s="47">
+        <f>COUNTIF('평가'!$P$6:$P$30,25)</f>
         <v/>
       </c>
     </row>
@@ -17706,9 +18820,9 @@
           <t>Group 1-24 columns count how many departments each respondent assigned to that group number.</t>
         </is>
       </c>
-      <c r="C17" s="34" t="n"/>
-      <c r="D17" s="34" t="n"/>
-      <c r="E17" s="34" t="n"/>
+      <c r="C17" s="50" t="n"/>
+      <c r="D17" s="50" t="n"/>
+      <c r="E17" s="51" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="33" t="inlineStr">
@@ -17721,9 +18835,9 @@
           <t>Number of non-empty group numbers used by the respondent.</t>
         </is>
       </c>
-      <c r="C18" s="34" t="n"/>
-      <c r="D18" s="34" t="n"/>
-      <c r="E18" s="34" t="n"/>
+      <c r="C18" s="50" t="n"/>
+      <c r="D18" s="50" t="n"/>
+      <c r="E18" s="51" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="33" t="inlineStr">
@@ -17736,9 +18850,9 @@
           <t>Size of the largest group. Review flags are not automatic exclusions.</t>
         </is>
       </c>
-      <c r="C19" s="34" t="n"/>
-      <c r="D19" s="34" t="n"/>
-      <c r="E19" s="34" t="n"/>
+      <c r="C19" s="50" t="n"/>
+      <c r="D19" s="50" t="n"/>
+      <c r="E19" s="51" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AC15"/>
